--- a/Financial Analysis/AML.xlsx
+++ b/Financial Analysis/AML.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200E1D0D-4F09-41D8-8BBC-D52D9DCDC57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F938C6-8D93-4716-AAA9-CD044AEF0B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
     <author>Anton Mniszek</author>
   </authors>
   <commentList>
-    <comment ref="AJ3" authorId="0" shapeId="0" xr:uid="{5E6EDA28-5391-4A42-AD3D-48740CD2223B}">
+    <comment ref="AN3" authorId="0" shapeId="0" xr:uid="{5E6EDA28-5391-4A42-AD3D-48740CD2223B}">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AM3" authorId="1" shapeId="0" xr:uid="{6F46B7D6-6A37-468F-80CB-B4D58BC38CA3}">
+    <comment ref="AQ3" authorId="1" shapeId="0" xr:uid="{6F46B7D6-6A37-468F-80CB-B4D58BC38CA3}">
       <text>
         <r>
           <rPr>
@@ -65,7 +65,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Anton Mniszek:</t>
         </r>
@@ -74,7 +74,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 c. £2.5 billion estimated for FY 27/28 in H224; believable?</t>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
   <si>
     <t>Q119</t>
   </si>
@@ -283,10 +283,19 @@
     <t>S&amp;M Margin</t>
   </si>
   <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
     <t>Overvalued</t>
-  </si>
-  <si>
-    <t>heavily depends on rev growth</t>
   </si>
 </sst>
 </file>
@@ -297,7 +306,7 @@
     <numFmt numFmtId="8" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
     <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,19 +348,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -419,14 +415,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
@@ -443,7 +439,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16009620" y="0"/>
+          <a:off x="18432780" y="0"/>
           <a:ext cx="0" cy="6103620"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -469,13 +465,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
@@ -493,8 +489,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21488400" y="0"/>
-          <a:ext cx="0" cy="5943600"/>
+          <a:off x="24536400" y="0"/>
+          <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -808,17 +804,17 @@
         <v>26</v>
       </c>
       <c r="D3" s="13">
-        <v>1.0980000000000001</v>
+        <v>0.71850000000000003</v>
       </c>
       <c r="E3" s="10">
-        <v>45635</v>
+        <v>45869</v>
       </c>
       <c r="F3" s="10">
         <f ca="1">TODAY()</f>
-        <v>45635</v>
+        <v>45899</v>
       </c>
       <c r="G3" s="10">
-        <v>45715</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -826,10 +822,10 @@
         <v>17</v>
       </c>
       <c r="D4" s="1">
-        <v>825</v>
+        <v>955.5</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -838,7 +834,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>905.85</v>
+        <v>686.52674999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -846,11 +842,11 @@
         <v>22</v>
       </c>
       <c r="D6" s="1">
-        <f>172.7+69.6</f>
-        <v>242.29999999999998</v>
+        <f>123.6+75.9</f>
+        <v>199.5</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -858,10 +854,10 @@
         <v>23</v>
       </c>
       <c r="D7" s="1">
-        <v>1216.5</v>
+        <v>1369.3</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -870,7 +866,7 @@
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>-974.2</v>
+        <v>-1169.8</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -879,7 +875,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D6+D7</f>
-        <v>1880.0500000000002</v>
+        <v>1856.3267499999999</v>
       </c>
     </row>
   </sheetData>
@@ -889,16 +885,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:DL28"/>
+  <dimension ref="A2:DP28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="45" width="8.88671875" customWidth="1"/>
-    <col min="48" max="48" width="14.6640625" customWidth="1"/>
-    <col min="49" max="49" width="12.109375" customWidth="1"/>
+    <col min="47" max="49" width="8.88671875" customWidth="1"/>
+    <col min="52" max="52" width="14.6640625" customWidth="1"/>
+    <col min="53" max="53" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:116" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:120" x14ac:dyDescent="0.3">
       <c r="D2" s="12" t="s">
         <v>0</v>
       </c>
@@ -971,62 +967,74 @@
       <c r="AA2" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="AC2">
+      <c r="AB2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC2" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD2" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG2">
         <v>2018</v>
       </c>
-      <c r="AD2">
+      <c r="AH2">
         <v>2019</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>2020</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <v>2021</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2022</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <v>2023</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>2024</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>2025</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <v>2026</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2027</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <v>2028</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <v>2029</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>2030</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>2031</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>2032</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>2033</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>2034</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="3:116" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:120" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1109,77 +1117,85 @@
         <f>W3*0.85</f>
         <v>504.30499999999995</v>
       </c>
-      <c r="AB3" s="3"/>
+      <c r="AB3" s="3">
+        <v>233.9</v>
+      </c>
       <c r="AC3" s="3">
+        <f>454.4-AB3</f>
+        <v>220.49999999999997</v>
+      </c>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3">
         <v>1096.5</v>
       </c>
-      <c r="AD3" s="3">
+      <c r="AH3" s="3">
         <f>SUM(D3:G3)</f>
         <v>997.3</v>
       </c>
-      <c r="AE3" s="3">
+      <c r="AI3" s="3">
         <f>SUM(H3:K3)</f>
         <v>611.79999999999995</v>
       </c>
-      <c r="AF3" s="3">
+      <c r="AJ3" s="3">
         <v>1095.3</v>
       </c>
-      <c r="AG3" s="3">
+      <c r="AK3" s="3">
         <v>1381.5</v>
       </c>
-      <c r="AH3" s="3">
+      <c r="AL3" s="3">
         <v>1632.8</v>
       </c>
-      <c r="AI3" s="3">
-        <f>SUM(X3:AA3)</f>
-        <v>1498.905</v>
-      </c>
-      <c r="AJ3" s="3">
-        <f>AI3*1.2</f>
-        <v>1798.6859999999999</v>
-      </c>
-      <c r="AK3" s="3">
-        <f>AJ3*1.14</f>
-        <v>2050.5020399999999</v>
-      </c>
-      <c r="AL3" s="3">
-        <f>AK3*1.1</f>
-        <v>2255.552244</v>
-      </c>
       <c r="AM3" s="3">
-        <f>AL3*1.08</f>
-        <v>2435.99642352</v>
+        <v>1583.9</v>
       </c>
       <c r="AN3" s="3">
-        <f>AM3*1.05</f>
-        <v>2557.796244696</v>
+        <f>AM3*1.03</f>
+        <v>1631.4170000000001</v>
       </c>
       <c r="AO3" s="3">
-        <f>AN3*1.04</f>
-        <v>2660.10809448384</v>
+        <f>AN3*1.25</f>
+        <v>2039.2712500000002</v>
       </c>
       <c r="AP3" s="3">
-        <f>AO3*1.03</f>
-        <v>2739.9113373183554</v>
+        <f>AO3*1.15</f>
+        <v>2345.1619375</v>
       </c>
       <c r="AQ3" s="3">
-        <f>AP3*1.03</f>
-        <v>2822.108677437906</v>
+        <f>AP3*1.1</f>
+        <v>2579.6781312500002</v>
       </c>
       <c r="AR3" s="3">
-        <f t="shared" ref="AR3:AT3" si="0">AQ3*1.03</f>
-        <v>2906.7719377610433</v>
+        <f>AQ3*1.05</f>
+        <v>2708.6620378125003</v>
       </c>
       <c r="AS3" s="3">
+        <f>AR3*1.04</f>
+        <v>2817.0085193250006</v>
+      </c>
+      <c r="AT3" s="3">
+        <f>AS3*1.03</f>
+        <v>2901.5187749047509</v>
+      </c>
+      <c r="AU3" s="3">
+        <f>AT3*1.03</f>
+        <v>2988.5643381518935</v>
+      </c>
+      <c r="AV3" s="3">
+        <f t="shared" ref="AV3:AX3" si="0">AU3*1.03</f>
+        <v>3078.2212682964505</v>
+      </c>
+      <c r="AW3" s="3">
         <f t="shared" si="0"/>
-        <v>2993.9750958938748</v>
-      </c>
-      <c r="AT3" s="3">
+        <v>3170.567906345344</v>
+      </c>
+      <c r="AX3" s="3">
         <f t="shared" si="0"/>
-        <v>3083.7943487706912</v>
+        <v>3265.6849435357044</v>
       </c>
     </row>
-    <row r="4" spans="3:116" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:120" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1259,76 +1275,84 @@
         <v>247.6</v>
       </c>
       <c r="AA4" s="1"/>
+      <c r="AB4" s="1">
+        <v>168.7</v>
+      </c>
       <c r="AC4" s="1">
+        <f>327.8-AB4</f>
+        <v>159.10000000000002</v>
+      </c>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AG4" s="1">
         <v>660.7</v>
       </c>
-      <c r="AD4" s="1">
+      <c r="AH4" s="1">
         <f>SUM(D4:G4)</f>
         <v>642.70000000000005</v>
       </c>
-      <c r="AE4" s="1">
+      <c r="AI4" s="1">
         <f>SUM(H4:K4)</f>
         <v>500.70000000000005</v>
       </c>
-      <c r="AF4" s="1">
+      <c r="AJ4" s="1">
         <v>751.6</v>
       </c>
-      <c r="AG4" s="1">
+      <c r="AK4" s="1">
         <v>930.8</v>
       </c>
-      <c r="AH4" s="1">
+      <c r="AL4" s="1">
         <v>993.6</v>
       </c>
-      <c r="AI4" s="1">
-        <f t="shared" ref="AI4:AO4" si="1">AI3-AI5</f>
-        <v>914.33204999999998</v>
-      </c>
-      <c r="AJ4" s="1">
-        <f t="shared" si="1"/>
-        <v>1043.2378800000001</v>
-      </c>
-      <c r="AK4" s="1">
-        <f t="shared" si="1"/>
-        <v>1168.7861628000001</v>
-      </c>
-      <c r="AL4" s="1">
-        <f t="shared" si="1"/>
-        <v>1263.10925664</v>
-      </c>
       <c r="AM4" s="1">
-        <f t="shared" si="1"/>
-        <v>1364.1579971711999</v>
+        <v>1000</v>
       </c>
       <c r="AN4" s="1">
-        <f t="shared" si="1"/>
-        <v>1432.3658970297599</v>
+        <f t="shared" ref="AN4:AS4" si="1">AN3-AN5</f>
+        <v>1027.7927100000002</v>
       </c>
       <c r="AO4" s="1">
         <f t="shared" si="1"/>
-        <v>1489.6605329109505</v>
+        <v>1223.5627500000001</v>
       </c>
       <c r="AP4" s="1">
-        <f t="shared" ref="AP4" si="2">AP3-AP5</f>
-        <v>1534.350348898279</v>
+        <f t="shared" si="1"/>
+        <v>1360.1939237500001</v>
       </c>
       <c r="AQ4" s="1">
-        <f t="shared" ref="AQ4:AT4" si="3">AQ3-AQ5</f>
-        <v>1580.3808593652273</v>
+        <f t="shared" si="1"/>
+        <v>1470.4165348125002</v>
       </c>
       <c r="AR4" s="1">
+        <f t="shared" si="1"/>
+        <v>1516.8507411750002</v>
+      </c>
+      <c r="AS4" s="1">
+        <f t="shared" si="1"/>
+        <v>1577.5247708220004</v>
+      </c>
+      <c r="AT4" s="1">
+        <f t="shared" ref="AT4" si="2">AT3-AT5</f>
+        <v>1624.8505139466604</v>
+      </c>
+      <c r="AU4" s="1">
+        <f t="shared" ref="AU4:AX4" si="3">AU3-AU5</f>
+        <v>1673.5960293650603</v>
+      </c>
+      <c r="AV4" s="1">
         <f t="shared" si="3"/>
-        <v>1627.7922851461842</v>
-      </c>
-      <c r="AS4" s="1">
+        <v>1723.8039102460123</v>
+      </c>
+      <c r="AW4" s="1">
         <f t="shared" si="3"/>
-        <v>1676.6260537005699</v>
-      </c>
-      <c r="AT4" s="1">
+        <v>1775.5180275533926</v>
+      </c>
+      <c r="AX4" s="1">
         <f t="shared" si="3"/>
-        <v>1726.924835311587</v>
+        <v>1828.7835683799944</v>
       </c>
     </row>
-    <row r="5" spans="3:116" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:120" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1428,80 +1452,90 @@
         <f>AA3*0.45</f>
         <v>226.93724999999998</v>
       </c>
+      <c r="AB5" s="3">
+        <f>AB3-AB4</f>
+        <v>65.200000000000017</v>
+      </c>
       <c r="AC5" s="3">
-        <f t="shared" ref="AC5" si="10">AC3-AC4</f>
+        <f>AC3-AC4</f>
+        <v>61.399999999999949</v>
+      </c>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AG5" s="3">
+        <f t="shared" ref="AG5" si="10">AG3-AG4</f>
         <v>435.79999999999995</v>
       </c>
-      <c r="AD5" s="3">
-        <f>AD3-AD4</f>
+      <c r="AH5" s="3">
+        <f t="shared" ref="AH5:AM5" si="11">AH3-AH4</f>
         <v>354.59999999999991</v>
       </c>
-      <c r="AE5" s="3">
-        <f>AE3-AE4</f>
+      <c r="AI5" s="3">
+        <f t="shared" si="11"/>
         <v>111.09999999999991</v>
       </c>
-      <c r="AF5" s="3">
-        <f>AF3-AF4</f>
+      <c r="AJ5" s="3">
+        <f t="shared" si="11"/>
         <v>343.69999999999993</v>
       </c>
-      <c r="AG5" s="3">
-        <f>AG3-AG4</f>
+      <c r="AK5" s="3">
+        <f t="shared" si="11"/>
         <v>450.70000000000005</v>
       </c>
-      <c r="AH5" s="3">
-        <f>AH3-AH4</f>
+      <c r="AL5" s="3">
+        <f t="shared" si="11"/>
         <v>639.19999999999993</v>
       </c>
-      <c r="AI5" s="3">
-        <f>AI3*0.39</f>
-        <v>584.57294999999999</v>
-      </c>
-      <c r="AJ5" s="3">
-        <f>AJ3*0.42</f>
-        <v>755.4481199999999</v>
-      </c>
-      <c r="AK5" s="3">
-        <f>AK3*0.43</f>
-        <v>881.71587719999991</v>
-      </c>
-      <c r="AL5" s="3">
-        <f>AL3*0.44</f>
-        <v>992.44298735999996</v>
-      </c>
       <c r="AM5" s="3">
-        <f t="shared" ref="AM5:AT5" si="11">AM3*0.44</f>
-        <v>1071.8384263488001</v>
+        <f t="shared" si="11"/>
+        <v>583.90000000000009</v>
       </c>
       <c r="AN5" s="3">
-        <f t="shared" si="11"/>
-        <v>1125.4303476662401</v>
+        <f>AN3*0.37</f>
+        <v>603.62429000000009</v>
       </c>
       <c r="AO5" s="3">
-        <f t="shared" si="11"/>
-        <v>1170.4475615728895</v>
+        <f>AO3*0.4</f>
+        <v>815.70850000000019</v>
       </c>
       <c r="AP5" s="3">
-        <f t="shared" si="11"/>
-        <v>1205.5609884200765</v>
+        <f>AP3*0.42</f>
+        <v>984.96801374999995</v>
       </c>
       <c r="AQ5" s="3">
-        <f t="shared" si="11"/>
-        <v>1241.7278180726787</v>
+        <f>AQ3*0.43</f>
+        <v>1109.2615964375</v>
       </c>
       <c r="AR5" s="3">
-        <f t="shared" si="11"/>
-        <v>1278.9796526148591</v>
+        <f t="shared" ref="AR5:AX5" si="12">AR3*0.44</f>
+        <v>1191.8112966375002</v>
       </c>
       <c r="AS5" s="3">
-        <f t="shared" si="11"/>
-        <v>1317.349042193305</v>
+        <f t="shared" si="12"/>
+        <v>1239.4837485030002</v>
       </c>
       <c r="AT5" s="3">
-        <f t="shared" si="11"/>
-        <v>1356.8695134591042</v>
+        <f t="shared" si="12"/>
+        <v>1276.6682609580905</v>
+      </c>
+      <c r="AU5" s="3">
+        <f t="shared" si="12"/>
+        <v>1314.9683087868332</v>
+      </c>
+      <c r="AV5" s="3">
+        <f t="shared" si="12"/>
+        <v>1354.4173580504382</v>
+      </c>
+      <c r="AW5" s="3">
+        <f t="shared" si="12"/>
+        <v>1395.0498787919514</v>
+      </c>
+      <c r="AX5" s="3">
+        <f t="shared" si="12"/>
+        <v>1436.90137515571</v>
       </c>
     </row>
-    <row r="6" spans="3:116" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:120" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>62</v>
       </c>
@@ -1568,77 +1602,85 @@
         <v>66.900000000000006</v>
       </c>
       <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
+      <c r="AA6" s="1">
+        <f>AM6-Y6</f>
+        <v>68.5</v>
+      </c>
+      <c r="AB6" s="1"/>
       <c r="AC6" s="1">
+        <v>54.1</v>
+      </c>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AG6" s="1">
         <f>89.8+293.2-20</f>
         <v>363</v>
       </c>
-      <c r="AD6" s="1">
+      <c r="AH6" s="1">
         <f>SUM(D6:G6)</f>
         <v>391.29999999999995</v>
       </c>
-      <c r="AE6" s="1">
+      <c r="AI6" s="1">
         <v>79.599999999999994</v>
       </c>
-      <c r="AF6" s="1">
+      <c r="AJ6" s="1">
         <v>84.8</v>
       </c>
-      <c r="AG6" s="1">
+      <c r="AK6" s="1">
         <v>113</v>
       </c>
-      <c r="AH6" s="1">
+      <c r="AL6" s="1">
         <v>143.80000000000001</v>
       </c>
-      <c r="AI6" s="1">
-        <f>AI3*0.09</f>
-        <v>134.90144999999998</v>
-      </c>
-      <c r="AJ6" s="1">
-        <f>AJ3*0.09</f>
-        <v>161.88173999999998</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ref="AK6:AT6" si="12">AK3*0.08</f>
-        <v>164.04016319999999</v>
-      </c>
-      <c r="AL6" s="1">
-        <f t="shared" si="12"/>
-        <v>180.44417952000001</v>
-      </c>
       <c r="AM6" s="1">
-        <f t="shared" si="12"/>
-        <v>194.8797138816</v>
+        <v>135.4</v>
       </c>
       <c r="AN6" s="1">
-        <f t="shared" si="12"/>
-        <v>204.62369957568001</v>
+        <f>AN3*0.09</f>
+        <v>146.82753</v>
       </c>
       <c r="AO6" s="1">
-        <f t="shared" si="12"/>
-        <v>212.80864755870721</v>
+        <f t="shared" ref="AO6:AX6" si="13">AO3*0.08</f>
+        <v>163.14170000000001</v>
       </c>
       <c r="AP6" s="1">
-        <f t="shared" si="12"/>
-        <v>219.19290698546843</v>
+        <f t="shared" si="13"/>
+        <v>187.612955</v>
       </c>
       <c r="AQ6" s="1">
-        <f t="shared" si="12"/>
-        <v>225.76869419503248</v>
+        <f t="shared" si="13"/>
+        <v>206.37425050000002</v>
       </c>
       <c r="AR6" s="1">
-        <f t="shared" si="12"/>
-        <v>232.54175502088347</v>
+        <f t="shared" si="13"/>
+        <v>216.69296302500004</v>
       </c>
       <c r="AS6" s="1">
-        <f t="shared" si="12"/>
-        <v>239.51800767150999</v>
+        <f t="shared" si="13"/>
+        <v>225.36068154600005</v>
       </c>
       <c r="AT6" s="1">
-        <f t="shared" si="12"/>
-        <v>246.7035479016553</v>
+        <f t="shared" si="13"/>
+        <v>232.12150199238008</v>
+      </c>
+      <c r="AU6" s="1">
+        <f t="shared" si="13"/>
+        <v>239.08514705215148</v>
+      </c>
+      <c r="AV6" s="1">
+        <f t="shared" si="13"/>
+        <v>246.25770146371605</v>
+      </c>
+      <c r="AW6" s="1">
+        <f t="shared" si="13"/>
+        <v>253.64543250762753</v>
+      </c>
+      <c r="AX6" s="1">
+        <f t="shared" si="13"/>
+        <v>261.25479548285637</v>
       </c>
     </row>
-    <row r="7" spans="3:116" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:120" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
         <v>61</v>
       </c>
@@ -1681,108 +1723,116 @@
         <v>272.10000000000002</v>
       </c>
       <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AC7" s="1"/>
+      <c r="AA7" s="1">
+        <f>AM7-Y7</f>
+        <v>275.89999999999998</v>
+      </c>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1">
+        <v>207.2</v>
+      </c>
       <c r="AD7" s="1"/>
-      <c r="AE7" s="1">
+      <c r="AE7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1">
         <v>354.4</v>
       </c>
-      <c r="AF7" s="1">
+      <c r="AJ7" s="1">
         <v>335.4</v>
       </c>
-      <c r="AG7" s="1">
+      <c r="AK7" s="1">
         <v>479.5</v>
       </c>
-      <c r="AH7" s="1">
+      <c r="AL7" s="1">
         <v>606.6</v>
       </c>
-      <c r="AI7" s="1">
-        <f>AH7*1.05</f>
-        <v>636.93000000000006</v>
-      </c>
-      <c r="AJ7" s="1">
-        <f>AI7*1.03</f>
-        <v>656.03790000000004</v>
-      </c>
-      <c r="AK7" s="1">
-        <f>AJ7*1.02</f>
-        <v>669.15865800000006</v>
-      </c>
-      <c r="AL7" s="1">
-        <f>AK7*1.01</f>
-        <v>675.85024458000009</v>
-      </c>
       <c r="AM7" s="1">
-        <f t="shared" ref="AM7:AT7" si="13">AL7*1.01</f>
-        <v>682.60874702580008</v>
+        <v>548</v>
       </c>
       <c r="AN7" s="1">
-        <f t="shared" si="13"/>
-        <v>689.4348344960581</v>
+        <f>AM7*0.88</f>
+        <v>482.24</v>
       </c>
       <c r="AO7" s="1">
-        <f t="shared" si="13"/>
-        <v>696.32918284101868</v>
+        <f>AN7*1.04</f>
+        <v>501.52960000000002</v>
       </c>
       <c r="AP7" s="1">
-        <f t="shared" si="13"/>
-        <v>703.29247466942888</v>
+        <f>AO7*1.03</f>
+        <v>516.57548800000006</v>
       </c>
       <c r="AQ7" s="1">
-        <f t="shared" si="13"/>
-        <v>710.32539941612322</v>
+        <f>AP7*1.02</f>
+        <v>526.90699776000008</v>
       </c>
       <c r="AR7" s="1">
-        <f t="shared" si="13"/>
-        <v>717.42865341028448</v>
+        <f t="shared" ref="AR7:AX7" si="14">AQ7*1.02</f>
+        <v>537.44513771520008</v>
       </c>
       <c r="AS7" s="1">
-        <f t="shared" si="13"/>
-        <v>724.60293994438734</v>
+        <f t="shared" si="14"/>
+        <v>548.1940404695041</v>
       </c>
       <c r="AT7" s="1">
-        <f t="shared" si="13"/>
-        <v>731.84896934383119</v>
+        <f t="shared" si="14"/>
+        <v>559.15792127889415</v>
+      </c>
+      <c r="AU7" s="1">
+        <f t="shared" si="14"/>
+        <v>570.34107970447201</v>
+      </c>
+      <c r="AV7" s="1">
+        <f t="shared" si="14"/>
+        <v>581.74790129856149</v>
+      </c>
+      <c r="AW7" s="1">
+        <f t="shared" si="14"/>
+        <v>593.38285932453277</v>
+      </c>
+      <c r="AX7" s="1">
+        <f t="shared" si="14"/>
+        <v>605.25051651102342</v>
       </c>
     </row>
-    <row r="8" spans="3:116" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:120" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" ref="D8:L8" si="14">D5-D6</f>
+        <f t="shared" ref="D8:L8" si="15">D5-D6</f>
         <v>-3.2000000000000028</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-34.499999999999957</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.5</v>
       </c>
       <c r="G8" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-9.5000000000000995</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-75.800000000000011</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-83.5</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-69.699999999999989</v>
       </c>
       <c r="K8" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-93.9</v>
       </c>
       <c r="L8" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-15.299999999999983</v>
       </c>
       <c r="M8" s="3"/>
@@ -1796,84 +1846,98 @@
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
+      <c r="X8" s="3">
+        <v>-58.7</v>
+      </c>
+      <c r="Y8" s="3">
+        <f>-272.1-X8</f>
+        <v>-213.40000000000003</v>
+      </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
+      <c r="AB8" s="3">
+        <v>-67.3</v>
+      </c>
       <c r="AC8" s="3">
-        <f t="shared" ref="AC8" si="15">AC5-AC6</f>
+        <f>-134.7-AB8</f>
+        <v>-67.399999999999991</v>
+      </c>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AG8" s="3">
+        <f t="shared" ref="AG8" si="16">AG5-AG6</f>
         <v>72.799999999999955</v>
       </c>
-      <c r="AD8" s="3">
-        <f>AD5-AD6</f>
+      <c r="AH8" s="3">
+        <f>AH5-AH6</f>
         <v>-36.700000000000045</v>
       </c>
-      <c r="AE8" s="3">
-        <f>AE5-AE6-AE7</f>
+      <c r="AI8" s="3">
+        <f>AI5-AI6-AI7</f>
         <v>-322.90000000000009</v>
       </c>
-      <c r="AF8" s="3">
-        <f>AF5-AF6-AF7</f>
+      <c r="AJ8" s="3">
+        <f>AJ5-AJ6-AJ7</f>
         <v>-76.500000000000057</v>
       </c>
-      <c r="AG8" s="3">
-        <f>AG5-AG6-AG7</f>
+      <c r="AK8" s="3">
+        <f>AK5-AK6-AK7</f>
         <v>-141.79999999999995</v>
       </c>
-      <c r="AH8" s="3">
-        <f>AH5-AH6-AH7</f>
+      <c r="AL8" s="3">
+        <f>AL5-AL6-AL7</f>
         <v>-111.2000000000001</v>
       </c>
-      <c r="AI8" s="3">
-        <f t="shared" ref="AI8:AT8" si="16">AI5-AI6-AI7</f>
-        <v>-187.25850000000003</v>
-      </c>
-      <c r="AJ8" s="3">
-        <f t="shared" si="16"/>
-        <v>-62.471520000000055</v>
-      </c>
-      <c r="AK8" s="3">
-        <f t="shared" si="16"/>
-        <v>48.517055999999911</v>
-      </c>
-      <c r="AL8" s="3">
-        <f t="shared" si="16"/>
-        <v>136.14856325999983</v>
-      </c>
       <c r="AM8" s="3">
-        <f t="shared" si="16"/>
-        <v>194.34996544140006</v>
+        <f t="shared" ref="AM8:AX8" si="17">AM5-AM6-AM7</f>
+        <v>-99.499999999999886</v>
       </c>
       <c r="AN8" s="3">
-        <f t="shared" si="16"/>
-        <v>231.37181359450199</v>
+        <f t="shared" si="17"/>
+        <v>-25.443239999999946</v>
       </c>
       <c r="AO8" s="3">
-        <f t="shared" si="16"/>
-        <v>261.30973117316364</v>
+        <f t="shared" si="17"/>
+        <v>151.03720000000015</v>
       </c>
       <c r="AP8" s="3">
-        <f t="shared" si="16"/>
-        <v>283.07560676517915</v>
+        <f t="shared" si="17"/>
+        <v>280.77957074999983</v>
       </c>
       <c r="AQ8" s="3">
-        <f t="shared" si="16"/>
-        <v>305.633724461523</v>
+        <f t="shared" si="17"/>
+        <v>375.98034817749988</v>
       </c>
       <c r="AR8" s="3">
-        <f t="shared" si="16"/>
-        <v>329.00924418369107</v>
+        <f t="shared" si="17"/>
+        <v>437.67319589730005</v>
       </c>
       <c r="AS8" s="3">
-        <f t="shared" si="16"/>
-        <v>353.22809457740755</v>
+        <f t="shared" si="17"/>
+        <v>465.92902648749612</v>
       </c>
       <c r="AT8" s="3">
-        <f t="shared" si="16"/>
-        <v>378.31699621361759</v>
+        <f t="shared" si="17"/>
+        <v>485.38883768681637</v>
+      </c>
+      <c r="AU8" s="3">
+        <f t="shared" si="17"/>
+        <v>505.5420820302096</v>
+      </c>
+      <c r="AV8" s="3">
+        <f t="shared" si="17"/>
+        <v>526.41175528816063</v>
+      </c>
+      <c r="AW8" s="3">
+        <f t="shared" si="17"/>
+        <v>548.02158695979119</v>
+      </c>
+      <c r="AX8" s="3">
+        <f t="shared" si="17"/>
+        <v>570.39606316183006</v>
       </c>
     </row>
-    <row r="9" spans="3:116" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:120" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1922,76 +1986,79 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
-      <c r="AC9" s="1">
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AG9" s="1">
         <v>-4.2</v>
       </c>
-      <c r="AD9" s="1">
+      <c r="AH9" s="1">
         <f>SUM(D9:G9)</f>
         <v>-16.3</v>
       </c>
-      <c r="AE9" s="1">
+      <c r="AI9" s="1">
         <f>SUM(H9:K9)</f>
         <v>-40</v>
       </c>
-      <c r="AF9" s="1">
+      <c r="AJ9" s="1">
         <v>-36.4</v>
       </c>
-      <c r="AG9" s="1">
+      <c r="AK9" s="1">
         <v>-15.5</v>
       </c>
-      <c r="AH9" s="1">
+      <c r="AL9" s="1">
         <v>-74.3</v>
       </c>
-      <c r="AI9" s="1">
-        <f>AH9-AH15*0.01</f>
-        <v>-72.018999999999991</v>
-      </c>
-      <c r="AJ9" s="1">
-        <f t="shared" ref="AJ9:AP9" si="17">AI9-AI15*0.01</f>
-        <v>-69.622553999999994</v>
-      </c>
-      <c r="AK9" s="1">
-        <f t="shared" si="17"/>
-        <v>-68.248922171999993</v>
-      </c>
-      <c r="AL9" s="1">
-        <f t="shared" si="17"/>
-        <v>-67.79458364037599</v>
-      </c>
       <c r="AM9" s="1">
-        <f t="shared" si="17"/>
-        <v>-68.078759474688994</v>
+        <v>-25.9</v>
       </c>
       <c r="AN9" s="1">
-        <f t="shared" si="17"/>
-        <v>-68.870678469008411</v>
+        <f t="shared" ref="AN9:AT9" si="18">AM9-AM15*0.01</f>
+        <v>-22.664999999999999</v>
       </c>
       <c r="AO9" s="1">
-        <f t="shared" si="17"/>
-        <v>-70.003764754868016</v>
+        <f t="shared" si="18"/>
+        <v>-20.970494079999998</v>
       </c>
       <c r="AP9" s="1">
-        <f t="shared" si="17"/>
-        <v>-71.422910829675885</v>
+        <f t="shared" si="18"/>
+        <v>-20.724444032640001</v>
       </c>
       <c r="AQ9" s="1">
-        <f t="shared" ref="AQ9" si="18">AP9-AP15*0.01</f>
-        <v>-73.063898344594605</v>
+        <f t="shared" si="18"/>
+        <v>-21.563027898901119</v>
       </c>
       <c r="AR9" s="1">
-        <f t="shared" ref="AR9" si="19">AQ9-AQ15*0.01</f>
-        <v>-74.933743334076382</v>
+        <f t="shared" si="18"/>
+        <v>-23.217130103072328</v>
       </c>
       <c r="AS9" s="1">
-        <f t="shared" ref="AS9" si="20">AR9-AR15*0.01</f>
-        <v>-77.039752081279104</v>
+        <f t="shared" si="18"/>
+        <v>-25.423795250768507</v>
       </c>
       <c r="AT9" s="1">
-        <f t="shared" ref="AT9" si="21">AS9-AS15*0.01</f>
-        <v>-79.389528604038475</v>
+        <f t="shared" si="18"/>
+        <v>-27.918574088177028</v>
+      </c>
+      <c r="AU9" s="1">
+        <f t="shared" ref="AU9" si="19">AT9-AT15*0.01</f>
+        <v>-30.632070957974307</v>
+      </c>
+      <c r="AV9" s="1">
+        <f t="shared" ref="AV9" si="20">AU9-AU15*0.01</f>
+        <v>-33.570290630209193</v>
+      </c>
+      <c r="AW9" s="1">
+        <f t="shared" ref="AW9" si="21">AV9-AV15*0.01</f>
+        <v>-36.739508652435681</v>
+      </c>
+      <c r="AX9" s="1">
+        <f t="shared" ref="AX9" si="22">AW9-AW15*0.01</f>
+        <v>-40.146278222566643</v>
       </c>
     </row>
-    <row r="10" spans="3:116" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:120" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
@@ -2046,114 +2113,117 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
-      <c r="AC10" s="1">
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AG10" s="1">
         <f>145.2</f>
         <v>145.19999999999999</v>
       </c>
-      <c r="AD10" s="1">
+      <c r="AH10" s="1">
         <f>SUM(D10:G10)</f>
         <v>83.9</v>
       </c>
-      <c r="AE10" s="1">
+      <c r="AI10" s="1">
         <f>SUM(H10:K10)</f>
         <v>183.10000000000002</v>
       </c>
-      <c r="AF10" s="1">
+      <c r="AJ10" s="1">
         <v>173.7</v>
       </c>
-      <c r="AG10" s="1">
+      <c r="AK10" s="1">
         <v>368.7</v>
       </c>
-      <c r="AH10" s="1">
+      <c r="AL10" s="1">
         <v>202.9</v>
       </c>
-      <c r="AI10" s="1">
-        <f>AH10*0.9</f>
-        <v>182.61</v>
-      </c>
-      <c r="AJ10" s="1">
-        <f>AI10*0.97</f>
-        <v>177.1317</v>
-      </c>
-      <c r="AK10" s="1">
-        <f t="shared" ref="AK10:AT10" si="22">AJ10*0.97</f>
-        <v>171.81774899999999</v>
-      </c>
-      <c r="AL10" s="1">
-        <f t="shared" si="22"/>
-        <v>166.66321653</v>
-      </c>
       <c r="AM10" s="1">
-        <f t="shared" si="22"/>
-        <v>161.6633200341</v>
+        <v>215.5</v>
       </c>
       <c r="AN10" s="1">
-        <f t="shared" si="22"/>
-        <v>156.813420433077</v>
+        <f>AM10*0.97</f>
+        <v>209.035</v>
       </c>
       <c r="AO10" s="1">
-        <f t="shared" si="22"/>
-        <v>152.10901782008469</v>
+        <f t="shared" ref="AO10:AX10" si="23">AN10*0.97</f>
+        <v>202.76394999999999</v>
       </c>
       <c r="AP10" s="1">
-        <f t="shared" si="22"/>
-        <v>147.54574728548215</v>
+        <f t="shared" si="23"/>
+        <v>196.68103149999999</v>
       </c>
       <c r="AQ10" s="1">
-        <f t="shared" si="22"/>
-        <v>143.1193748669177</v>
+        <f t="shared" si="23"/>
+        <v>190.78060055499998</v>
       </c>
       <c r="AR10" s="1">
-        <f t="shared" si="22"/>
-        <v>138.82579362091016</v>
+        <f t="shared" si="23"/>
+        <v>185.05718253834996</v>
       </c>
       <c r="AS10" s="1">
-        <f t="shared" si="22"/>
-        <v>134.66101981228286</v>
+        <f t="shared" si="23"/>
+        <v>179.50546706219947</v>
       </c>
       <c r="AT10" s="1">
-        <f t="shared" si="22"/>
-        <v>130.62118921791438</v>
+        <f t="shared" si="23"/>
+        <v>174.12030305033349</v>
+      </c>
+      <c r="AU10" s="1">
+        <f t="shared" si="23"/>
+        <v>168.89669395882348</v>
+      </c>
+      <c r="AV10" s="1">
+        <f t="shared" si="23"/>
+        <v>163.82979314005877</v>
+      </c>
+      <c r="AW10" s="1">
+        <f t="shared" si="23"/>
+        <v>158.91489934585701</v>
+      </c>
+      <c r="AX10" s="1">
+        <f t="shared" si="23"/>
+        <v>154.14745236548129</v>
       </c>
     </row>
-    <row r="11" spans="3:116" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:120" x14ac:dyDescent="0.3">
       <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" ref="D11:L11" si="23">D9+D10</f>
+        <f t="shared" ref="D11:L11" si="24">D9+D10</f>
         <v>14.1</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>27</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>24</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.5000000000000036</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>42.2</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>25.9</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10.7</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>64.300000000000011</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>26.9</v>
       </c>
       <c r="M11" s="1"/>
@@ -2171,117 +2241,121 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
-      <c r="AC11" s="1">
-        <f t="shared" ref="AC11" si="24">AC9+AC10</f>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AG11" s="1">
+        <f t="shared" ref="AG11" si="25">AG9+AG10</f>
         <v>141</v>
       </c>
-      <c r="AD11" s="1">
-        <f>AD9+AD10</f>
+      <c r="AH11" s="1">
+        <f>AH9+AH10</f>
         <v>67.600000000000009</v>
       </c>
-      <c r="AE11" s="1">
-        <f>AE9+AE10</f>
+      <c r="AI11" s="1">
+        <f>AI9+AI10</f>
         <v>143.10000000000002</v>
       </c>
-      <c r="AF11" s="1">
-        <f>AF9+AF10</f>
+      <c r="AJ11" s="1">
+        <f>AJ9+AJ10</f>
         <v>137.29999999999998</v>
       </c>
-      <c r="AG11" s="1">
-        <f t="shared" ref="AG11:AO11" si="25">AG9+AG10</f>
+      <c r="AK11" s="1">
+        <f t="shared" ref="AK11:AS11" si="26">AK9+AK10</f>
         <v>353.2</v>
       </c>
-      <c r="AH11" s="1">
-        <f t="shared" si="25"/>
+      <c r="AL11" s="1">
+        <f t="shared" si="26"/>
         <v>128.60000000000002</v>
       </c>
-      <c r="AI11" s="1">
-        <f t="shared" si="25"/>
-        <v>110.59100000000002</v>
-      </c>
-      <c r="AJ11" s="1">
-        <f t="shared" si="25"/>
-        <v>107.509146</v>
-      </c>
-      <c r="AK11" s="1">
-        <f t="shared" si="25"/>
-        <v>103.568826828</v>
-      </c>
-      <c r="AL11" s="1">
-        <f t="shared" si="25"/>
-        <v>98.86863288962401</v>
-      </c>
       <c r="AM11" s="1">
-        <f t="shared" si="25"/>
-        <v>93.584560559411003</v>
+        <f t="shared" si="26"/>
+        <v>189.6</v>
       </c>
       <c r="AN11" s="1">
-        <f t="shared" si="25"/>
-        <v>87.942741964068588</v>
+        <f t="shared" si="26"/>
+        <v>186.37</v>
       </c>
       <c r="AO11" s="1">
-        <f t="shared" si="25"/>
-        <v>82.105253065216672</v>
+        <f t="shared" si="26"/>
+        <v>181.79345591999999</v>
       </c>
       <c r="AP11" s="1">
-        <f t="shared" ref="AP11" si="26">AP9+AP10</f>
-        <v>76.122836455806265</v>
+        <f t="shared" si="26"/>
+        <v>175.95658746735998</v>
       </c>
       <c r="AQ11" s="1">
-        <f t="shared" ref="AQ11:AT11" si="27">AQ9+AQ10</f>
-        <v>70.05547652232309</v>
+        <f t="shared" si="26"/>
+        <v>169.21757265609887</v>
       </c>
       <c r="AR11" s="1">
-        <f t="shared" si="27"/>
-        <v>63.892050286833779</v>
+        <f t="shared" si="26"/>
+        <v>161.84005243527764</v>
       </c>
       <c r="AS11" s="1">
-        <f t="shared" si="27"/>
-        <v>57.621267731003755</v>
+        <f t="shared" si="26"/>
+        <v>154.08167181143097</v>
       </c>
       <c r="AT11" s="1">
-        <f t="shared" si="27"/>
-        <v>51.231660613875903</v>
+        <f t="shared" ref="AT11" si="27">AT9+AT10</f>
+        <v>146.20172896215647</v>
+      </c>
+      <c r="AU11" s="1">
+        <f t="shared" ref="AU11:AX11" si="28">AU9+AU10</f>
+        <v>138.26462300084916</v>
+      </c>
+      <c r="AV11" s="1">
+        <f t="shared" si="28"/>
+        <v>130.25950250984957</v>
+      </c>
+      <c r="AW11" s="1">
+        <f t="shared" si="28"/>
+        <v>122.17539069342132</v>
+      </c>
+      <c r="AX11" s="1">
+        <f t="shared" si="28"/>
+        <v>114.00117414291464</v>
       </c>
     </row>
-    <row r="12" spans="3:116" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:120" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="3">
-        <f t="shared" ref="D12:L12" si="28">D8-D11</f>
+        <f t="shared" ref="D12:L12" si="29">D8-D11</f>
         <v>-17.300000000000004</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-61.499999999999957</v>
       </c>
       <c r="F12" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-13.5</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-12.000000000000103</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-118.00000000000001</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-109.4</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-80.399999999999991</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-158.20000000000002</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-42.199999999999982</v>
       </c>
       <c r="M12" s="3"/>
@@ -2299,80 +2373,84 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
-      <c r="AC12" s="3">
-        <f t="shared" ref="AC12" si="29">AC8-AC11</f>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AG12" s="3">
+        <f t="shared" ref="AG12" si="30">AG8-AG11</f>
         <v>-68.200000000000045</v>
       </c>
-      <c r="AD12" s="3">
-        <f>AD8-AD11</f>
+      <c r="AH12" s="3">
+        <f>AH8-AH11</f>
         <v>-104.30000000000005</v>
       </c>
-      <c r="AE12" s="3">
-        <f>AE8-AE11</f>
+      <c r="AI12" s="3">
+        <f>AI8-AI11</f>
         <v>-466.00000000000011</v>
       </c>
-      <c r="AF12" s="3">
-        <f t="shared" ref="AF12:AO12" si="30">AF8-AF11</f>
+      <c r="AJ12" s="3">
+        <f t="shared" ref="AJ12:AS12" si="31">AJ8-AJ11</f>
         <v>-213.80000000000004</v>
       </c>
-      <c r="AG12" s="3">
-        <f t="shared" si="30"/>
+      <c r="AK12" s="3">
+        <f t="shared" si="31"/>
         <v>-494.99999999999994</v>
       </c>
-      <c r="AH12" s="3">
-        <f t="shared" si="30"/>
+      <c r="AL12" s="3">
+        <f t="shared" si="31"/>
         <v>-239.80000000000013</v>
       </c>
-      <c r="AI12" s="3">
-        <f t="shared" si="30"/>
-        <v>-297.84950000000003</v>
-      </c>
-      <c r="AJ12" s="3">
-        <f t="shared" si="30"/>
-        <v>-169.98066600000004</v>
-      </c>
-      <c r="AK12" s="3">
-        <f t="shared" si="30"/>
-        <v>-55.051770828000087</v>
-      </c>
-      <c r="AL12" s="3">
-        <f t="shared" si="30"/>
-        <v>37.279930370375823</v>
-      </c>
       <c r="AM12" s="3">
-        <f t="shared" si="30"/>
-        <v>100.76540488198906</v>
+        <f t="shared" si="31"/>
+        <v>-289.09999999999991</v>
       </c>
       <c r="AN12" s="3">
-        <f t="shared" si="30"/>
-        <v>143.42907163043338</v>
+        <f t="shared" si="31"/>
+        <v>-211.81323999999995</v>
       </c>
       <c r="AO12" s="3">
-        <f t="shared" si="30"/>
-        <v>179.20447810794695</v>
+        <f t="shared" si="31"/>
+        <v>-30.75625591999983</v>
       </c>
       <c r="AP12" s="3">
-        <f t="shared" ref="AP12" si="31">AP8-AP11</f>
-        <v>206.95277030937288</v>
+        <f t="shared" si="31"/>
+        <v>104.82298328263985</v>
       </c>
       <c r="AQ12" s="3">
-        <f t="shared" ref="AQ12:AT12" si="32">AQ8-AQ11</f>
-        <v>235.57824793919991</v>
+        <f t="shared" si="31"/>
+        <v>206.76277552140101</v>
       </c>
       <c r="AR12" s="3">
-        <f t="shared" si="32"/>
-        <v>265.11719389685732</v>
+        <f t="shared" si="31"/>
+        <v>275.83314346202241</v>
       </c>
       <c r="AS12" s="3">
-        <f t="shared" si="32"/>
-        <v>295.60682684640381</v>
+        <f t="shared" si="31"/>
+        <v>311.84735467606515</v>
       </c>
       <c r="AT12" s="3">
-        <f t="shared" si="32"/>
-        <v>327.08533559974171</v>
+        <f t="shared" ref="AT12" si="32">AT8-AT11</f>
+        <v>339.18710872465988</v>
+      </c>
+      <c r="AU12" s="3">
+        <f t="shared" ref="AU12:AX12" si="33">AU8-AU11</f>
+        <v>367.27745902936044</v>
+      </c>
+      <c r="AV12" s="3">
+        <f t="shared" si="33"/>
+        <v>396.15225277831109</v>
+      </c>
+      <c r="AW12" s="3">
+        <f t="shared" si="33"/>
+        <v>425.84619626636987</v>
+      </c>
+      <c r="AX12" s="3">
+        <f t="shared" si="33"/>
+        <v>456.39488901891542</v>
       </c>
     </row>
-    <row r="13" spans="3:116" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:120" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2422,76 +2500,79 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
-      <c r="AC13" s="1">
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AG13" s="1">
         <v>-11.1</v>
       </c>
-      <c r="AD13" s="1">
+      <c r="AH13" s="1">
         <f>SUM(D13:G13)</f>
         <v>0.10000000000000142</v>
       </c>
-      <c r="AE13" s="1">
+      <c r="AI13" s="1">
         <f>SUM(H13:K13)</f>
         <v>-55.600000000000009</v>
       </c>
-      <c r="AF13" s="1">
+      <c r="AJ13" s="1">
         <v>-24.5</v>
       </c>
-      <c r="AG13" s="1">
+      <c r="AK13" s="1">
         <v>32.700000000000003</v>
       </c>
-      <c r="AH13" s="1">
+      <c r="AL13" s="1">
         <v>-13</v>
       </c>
-      <c r="AI13" s="1">
-        <f t="shared" ref="AI13:AO13" si="33">AI12*0.2</f>
-        <v>-59.569900000000011</v>
-      </c>
-      <c r="AJ13" s="1">
-        <f t="shared" si="33"/>
-        <v>-33.99613320000001</v>
-      </c>
-      <c r="AK13" s="1">
-        <f t="shared" si="33"/>
-        <v>-11.010354165600019</v>
-      </c>
-      <c r="AL13" s="1">
-        <f t="shared" si="33"/>
-        <v>7.4559860740751649</v>
-      </c>
       <c r="AM13" s="1">
-        <f t="shared" si="33"/>
-        <v>20.153080976397813</v>
+        <v>34.4</v>
       </c>
       <c r="AN13" s="1">
-        <f t="shared" si="33"/>
-        <v>28.685814326086678</v>
+        <f t="shared" ref="AN13:AS13" si="34">AN12*0.2</f>
+        <v>-42.362647999999993</v>
       </c>
       <c r="AO13" s="1">
-        <f t="shared" si="33"/>
-        <v>35.840895621589389</v>
+        <f t="shared" si="34"/>
+        <v>-6.1512511839999666</v>
       </c>
       <c r="AP13" s="1">
-        <f t="shared" ref="AP13" si="34">AP12*0.2</f>
-        <v>41.390554061874582</v>
+        <f t="shared" si="34"/>
+        <v>20.964596656527974</v>
       </c>
       <c r="AQ13" s="1">
-        <f t="shared" ref="AQ13:AT13" si="35">AQ12*0.2</f>
-        <v>47.115649587839982</v>
+        <f t="shared" si="34"/>
+        <v>41.352555104280206</v>
       </c>
       <c r="AR13" s="1">
-        <f t="shared" si="35"/>
-        <v>53.023438779371467</v>
+        <f t="shared" si="34"/>
+        <v>55.166628692404487</v>
       </c>
       <c r="AS13" s="1">
-        <f t="shared" si="35"/>
-        <v>59.121365369280767</v>
+        <f t="shared" si="34"/>
+        <v>62.36947093521303</v>
       </c>
       <c r="AT13" s="1">
-        <f t="shared" si="35"/>
-        <v>65.417067119948342</v>
+        <f t="shared" ref="AT13" si="35">AT12*0.2</f>
+        <v>67.837421744931973</v>
+      </c>
+      <c r="AU13" s="1">
+        <f t="shared" ref="AU13:AX13" si="36">AU12*0.2</f>
+        <v>73.455491805872086</v>
+      </c>
+      <c r="AV13" s="1">
+        <f t="shared" si="36"/>
+        <v>79.23045055566223</v>
+      </c>
+      <c r="AW13" s="1">
+        <f t="shared" si="36"/>
+        <v>85.169239253273986</v>
+      </c>
+      <c r="AX13" s="1">
+        <f t="shared" si="36"/>
+        <v>91.278977803783093</v>
       </c>
     </row>
-    <row r="14" spans="3:116" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:120" x14ac:dyDescent="0.3">
       <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
@@ -2540,105 +2621,97 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
-      <c r="AC14" s="1">
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AG14" s="1">
         <v>5.6</v>
       </c>
-      <c r="AD14" s="1">
+      <c r="AH14" s="1">
         <f>SUM(D14:G14)</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="AE14" s="1">
+      <c r="AI14" s="1">
         <f>SUM(H14:K14)</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="AF14" s="1">
+      <c r="AJ14" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AG14" s="1">
+      <c r="AK14" s="1">
         <v>0.9</v>
       </c>
-      <c r="AH14" s="1">
+      <c r="AL14" s="1">
         <v>1.3</v>
       </c>
-      <c r="AI14" s="1">
-        <f>AH14*1.05</f>
-        <v>1.3650000000000002</v>
-      </c>
-      <c r="AJ14" s="1">
-        <f>AI14*1.01</f>
-        <v>1.3786500000000002</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ref="AK14:AP14" si="36">AJ14*1.01</f>
-        <v>1.3924365000000001</v>
-      </c>
-      <c r="AL14" s="1">
-        <f t="shared" si="36"/>
-        <v>1.4063608650000001</v>
-      </c>
       <c r="AM14" s="1">
-        <f t="shared" si="36"/>
-        <v>1.4204244736500002</v>
+        <v>0</v>
       </c>
       <c r="AN14" s="1">
-        <f t="shared" si="36"/>
-        <v>1.4346287183865003</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="1">
-        <f t="shared" si="36"/>
-        <v>1.4489750055703654</v>
+        <v>0</v>
       </c>
       <c r="AP14" s="1">
-        <f t="shared" si="36"/>
-        <v>1.4634647556260691</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="1">
-        <f t="shared" ref="AQ14" si="37">AP14*1.01</f>
-        <v>1.4780994031823298</v>
+        <v>0</v>
       </c>
       <c r="AR14" s="1">
-        <f t="shared" ref="AR14" si="38">AQ14*1.01</f>
-        <v>1.4928803972141531</v>
+        <v>0</v>
       </c>
       <c r="AS14" s="1">
-        <f t="shared" ref="AS14" si="39">AR14*1.01</f>
-        <v>1.5078092011862947</v>
+        <v>0</v>
       </c>
       <c r="AT14" s="1">
-        <f t="shared" ref="AT14" si="40">AS14*1.01</f>
-        <v>1.5228872931981576</v>
+        <v>0</v>
+      </c>
+      <c r="AU14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:116" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:120" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" ref="D15:J15" si="41">D12-D13-D14</f>
+        <f t="shared" ref="D15:J15" si="37">D12-D13-D14</f>
         <v>-13.900000000000004</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>-49.099999999999959</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>-10.1</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>-40.100000000000108</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>-100.00000000000001</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>-111.10000000000001</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>-67.999999999999986</v>
       </c>
       <c r="K15" s="3">
@@ -2646,7 +2719,7 @@
         <v>-140.10000000000002</v>
       </c>
       <c r="L15" s="3">
-        <f t="shared" ref="L15" si="42">L12-L13-L14</f>
+        <f t="shared" ref="L15" si="38">L12-L13-L14</f>
         <v>-42.59999999999998</v>
       </c>
       <c r="M15" s="3"/>
@@ -2660,364 +2733,378 @@
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
+      <c r="X15" s="3">
+        <v>-138.9</v>
+      </c>
+      <c r="Y15" s="3">
+        <f>-207.6-X15</f>
+        <v>-68.699999999999989</v>
+      </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
+      <c r="AB15" s="3">
+        <v>-80</v>
+      </c>
       <c r="AC15" s="3">
-        <f>AC12-AC13-AC14</f>
+        <f>-148.7-AB15</f>
+        <v>-68.699999999999989</v>
+      </c>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AG15" s="3">
+        <f>AG12-AG13-AG14</f>
         <v>-62.700000000000045</v>
       </c>
-      <c r="AD15" s="3">
-        <f>AD12-AD13-AD14</f>
+      <c r="AH15" s="3">
+        <f>AH12-AH13-AH14</f>
         <v>-113.20000000000006</v>
       </c>
-      <c r="AE15" s="3">
-        <f>AE12-AE13-AE14</f>
+      <c r="AI15" s="3">
+        <f>AI12-AI13-AI14</f>
         <v>-419.2000000000001</v>
       </c>
-      <c r="AF15" s="3">
-        <f t="shared" ref="AF15:AO15" si="43">AF12-AF13-AF14</f>
+      <c r="AJ15" s="3">
+        <f t="shared" ref="AJ15:AS15" si="39">AJ12-AJ13-AJ14</f>
         <v>-191.60000000000005</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AK15" s="3">
+        <f t="shared" si="39"/>
+        <v>-528.59999999999991</v>
+      </c>
+      <c r="AL15" s="3">
+        <f t="shared" si="39"/>
+        <v>-228.10000000000014</v>
+      </c>
+      <c r="AM15" s="3">
+        <f t="shared" si="39"/>
+        <v>-323.49999999999989</v>
+      </c>
+      <c r="AN15" s="3">
+        <f t="shared" si="39"/>
+        <v>-169.45059199999997</v>
+      </c>
+      <c r="AO15" s="3">
+        <f t="shared" si="39"/>
+        <v>-24.605004735999863</v>
+      </c>
+      <c r="AP15" s="3">
+        <f t="shared" si="39"/>
+        <v>83.85838662611188</v>
+      </c>
+      <c r="AQ15" s="3">
+        <f t="shared" si="39"/>
+        <v>165.4102204171208</v>
+      </c>
+      <c r="AR15" s="3">
+        <f t="shared" si="39"/>
+        <v>220.66651476961792</v>
+      </c>
+      <c r="AS15" s="3">
+        <f t="shared" si="39"/>
+        <v>249.47788374085212</v>
+      </c>
+      <c r="AT15" s="3">
+        <f t="shared" ref="AT15" si="40">AT12-AT13-AT14</f>
+        <v>271.34968697972789</v>
+      </c>
+      <c r="AU15" s="3">
+        <f t="shared" ref="AU15:AX15" si="41">AU12-AU13-AU14</f>
+        <v>293.82196722348834</v>
+      </c>
+      <c r="AV15" s="3">
+        <f t="shared" si="41"/>
+        <v>316.92180222264886</v>
+      </c>
+      <c r="AW15" s="3">
+        <f t="shared" si="41"/>
+        <v>340.67695701309589</v>
+      </c>
+      <c r="AX15" s="3">
+        <f t="shared" si="41"/>
+        <v>365.11591121513231</v>
+      </c>
+      <c r="AY15" s="3">
+        <f>AX15*(1+$BA$18)</f>
+        <v>361.46475210298098</v>
+      </c>
+      <c r="AZ15" s="3">
+        <f t="shared" ref="AZ15:DK15" si="42">AY15*(1+$BA$18)</f>
+        <v>357.85010458195114</v>
+      </c>
+      <c r="BA15" s="3">
+        <f t="shared" si="42"/>
+        <v>354.27160353613164</v>
+      </c>
+      <c r="BB15" s="3">
+        <f t="shared" si="42"/>
+        <v>350.72888750077033</v>
+      </c>
+      <c r="BC15" s="3">
+        <f t="shared" si="42"/>
+        <v>347.22159862576262</v>
+      </c>
+      <c r="BD15" s="3">
+        <f t="shared" si="42"/>
+        <v>343.74938263950497</v>
+      </c>
+      <c r="BE15" s="3">
+        <f t="shared" si="42"/>
+        <v>340.31188881310993</v>
+      </c>
+      <c r="BF15" s="3">
+        <f t="shared" si="42"/>
+        <v>336.90876992497886</v>
+      </c>
+      <c r="BG15" s="3">
+        <f t="shared" si="42"/>
+        <v>333.53968222572905</v>
+      </c>
+      <c r="BH15" s="3">
+        <f t="shared" si="42"/>
+        <v>330.20428540347177</v>
+      </c>
+      <c r="BI15" s="3">
+        <f t="shared" si="42"/>
+        <v>326.90224254943706</v>
+      </c>
+      <c r="BJ15" s="3">
+        <f t="shared" si="42"/>
+        <v>323.63322012394269</v>
+      </c>
+      <c r="BK15" s="3">
+        <f t="shared" si="42"/>
+        <v>320.39688792270329</v>
+      </c>
+      <c r="BL15" s="3">
+        <f t="shared" si="42"/>
+        <v>317.19291904347625</v>
+      </c>
+      <c r="BM15" s="3">
+        <f t="shared" si="42"/>
+        <v>314.0209898530415</v>
+      </c>
+      <c r="BN15" s="3">
+        <f t="shared" si="42"/>
+        <v>310.88077995451107</v>
+      </c>
+      <c r="BO15" s="3">
+        <f t="shared" si="42"/>
+        <v>307.77197215496597</v>
+      </c>
+      <c r="BP15" s="3">
+        <f t="shared" si="42"/>
+        <v>304.6942524334163</v>
+      </c>
+      <c r="BQ15" s="3">
+        <f t="shared" si="42"/>
+        <v>301.64730990908214</v>
+      </c>
+      <c r="BR15" s="3">
+        <f t="shared" si="42"/>
+        <v>298.63083680999131</v>
+      </c>
+      <c r="BS15" s="3">
+        <f t="shared" si="42"/>
+        <v>295.6445284418914</v>
+      </c>
+      <c r="BT15" s="3">
+        <f t="shared" si="42"/>
+        <v>292.68808315747248</v>
+      </c>
+      <c r="BU15" s="3">
+        <f t="shared" si="42"/>
+        <v>289.76120232589773</v>
+      </c>
+      <c r="BV15" s="3">
+        <f t="shared" si="42"/>
+        <v>286.86359030263873</v>
+      </c>
+      <c r="BW15" s="3">
+        <f t="shared" si="42"/>
+        <v>283.99495439961231</v>
+      </c>
+      <c r="BX15" s="3">
+        <f t="shared" si="42"/>
+        <v>281.1550048556162</v>
+      </c>
+      <c r="BY15" s="3">
+        <f t="shared" si="42"/>
+        <v>278.34345480706003</v>
+      </c>
+      <c r="BZ15" s="3">
+        <f t="shared" si="42"/>
+        <v>275.56002025898943</v>
+      </c>
+      <c r="CA15" s="3">
+        <f t="shared" si="42"/>
+        <v>272.80442005639952</v>
+      </c>
+      <c r="CB15" s="3">
+        <f t="shared" si="42"/>
+        <v>270.07637585583552</v>
+      </c>
+      <c r="CC15" s="3">
+        <f t="shared" si="42"/>
+        <v>267.37561209727716</v>
+      </c>
+      <c r="CD15" s="3">
+        <f t="shared" si="42"/>
+        <v>264.70185597630439</v>
+      </c>
+      <c r="CE15" s="3">
+        <f t="shared" si="42"/>
+        <v>262.05483741654132</v>
+      </c>
+      <c r="CF15" s="3">
+        <f t="shared" si="42"/>
+        <v>259.43428904237589</v>
+      </c>
+      <c r="CG15" s="3">
+        <f t="shared" si="42"/>
+        <v>256.83994615195212</v>
+      </c>
+      <c r="CH15" s="3">
+        <f t="shared" si="42"/>
+        <v>254.27154669043259</v>
+      </c>
+      <c r="CI15" s="3">
+        <f t="shared" si="42"/>
+        <v>251.72883122352826</v>
+      </c>
+      <c r="CJ15" s="3">
+        <f t="shared" si="42"/>
+        <v>249.21154291129298</v>
+      </c>
+      <c r="CK15" s="3">
+        <f t="shared" si="42"/>
+        <v>246.71942748218004</v>
+      </c>
+      <c r="CL15" s="3">
+        <f t="shared" si="42"/>
+        <v>244.25223320735824</v>
+      </c>
+      <c r="CM15" s="3">
+        <f t="shared" si="42"/>
+        <v>241.80971087528465</v>
+      </c>
+      <c r="CN15" s="3">
+        <f t="shared" si="42"/>
+        <v>239.3916137665318</v>
+      </c>
+      <c r="CO15" s="3">
+        <f t="shared" si="42"/>
+        <v>236.99769762886649</v>
+      </c>
+      <c r="CP15" s="3">
+        <f t="shared" si="42"/>
+        <v>234.62772065257784</v>
+      </c>
+      <c r="CQ15" s="3">
+        <f t="shared" si="42"/>
+        <v>232.28144344605207</v>
+      </c>
+      <c r="CR15" s="3">
+        <f t="shared" si="42"/>
+        <v>229.95862901159154</v>
+      </c>
+      <c r="CS15" s="3">
+        <f t="shared" si="42"/>
+        <v>227.65904272147563</v>
+      </c>
+      <c r="CT15" s="3">
+        <f t="shared" si="42"/>
+        <v>225.38245229426087</v>
+      </c>
+      <c r="CU15" s="3">
+        <f t="shared" si="42"/>
+        <v>223.12862777131826</v>
+      </c>
+      <c r="CV15" s="3">
+        <f t="shared" si="42"/>
+        <v>220.89734149360507</v>
+      </c>
+      <c r="CW15" s="3">
+        <f t="shared" si="42"/>
+        <v>218.68836807866901</v>
+      </c>
+      <c r="CX15" s="3">
+        <f t="shared" si="42"/>
+        <v>216.50148439788234</v>
+      </c>
+      <c r="CY15" s="3">
+        <f t="shared" si="42"/>
+        <v>214.3364695539035</v>
+      </c>
+      <c r="CZ15" s="3">
+        <f t="shared" si="42"/>
+        <v>212.19310485836445</v>
+      </c>
+      <c r="DA15" s="3">
+        <f t="shared" si="42"/>
+        <v>210.07117380978082</v>
+      </c>
+      <c r="DB15" s="3">
+        <f t="shared" si="42"/>
+        <v>207.97046207168302</v>
+      </c>
+      <c r="DC15" s="3">
+        <f t="shared" si="42"/>
+        <v>205.89075745096619</v>
+      </c>
+      <c r="DD15" s="3">
+        <f t="shared" si="42"/>
+        <v>203.83184987645652</v>
+      </c>
+      <c r="DE15" s="3">
+        <f t="shared" si="42"/>
+        <v>201.79353137769195</v>
+      </c>
+      <c r="DF15" s="3">
+        <f t="shared" si="42"/>
+        <v>199.77559606391503</v>
+      </c>
+      <c r="DG15" s="3">
+        <f t="shared" si="42"/>
+        <v>197.77784010327588</v>
+      </c>
+      <c r="DH15" s="3">
+        <f t="shared" si="42"/>
+        <v>195.80006170224311</v>
+      </c>
+      <c r="DI15" s="3">
+        <f t="shared" si="42"/>
+        <v>193.84206108522068</v>
+      </c>
+      <c r="DJ15" s="3">
+        <f t="shared" si="42"/>
+        <v>191.90364047436847</v>
+      </c>
+      <c r="DK15" s="3">
+        <f t="shared" si="42"/>
+        <v>189.98460406962479</v>
+      </c>
+      <c r="DL15" s="3">
+        <f t="shared" ref="DL15:DP15" si="43">DK15*(1+$BA$18)</f>
+        <v>188.08475802892855</v>
+      </c>
+      <c r="DM15" s="3">
         <f t="shared" si="43"/>
-        <v>-528.59999999999991</v>
-      </c>
-      <c r="AH15" s="3">
+        <v>186.20391044863925</v>
+      </c>
+      <c r="DN15" s="3">
         <f t="shared" si="43"/>
-        <v>-228.10000000000014</v>
-      </c>
-      <c r="AI15" s="3">
+        <v>184.34187134415285</v>
+      </c>
+      <c r="DO15" s="3">
         <f t="shared" si="43"/>
-        <v>-239.64460000000003</v>
-      </c>
-      <c r="AJ15" s="3">
+        <v>182.49845263071131</v>
+      </c>
+      <c r="DP15" s="3">
         <f t="shared" si="43"/>
-        <v>-137.36318280000003</v>
-      </c>
-      <c r="AK15" s="3">
-        <f t="shared" si="43"/>
-        <v>-45.433853162400069</v>
-      </c>
-      <c r="AL15" s="3">
-        <f t="shared" si="43"/>
-        <v>28.41758343130066</v>
-      </c>
-      <c r="AM15" s="3">
-        <f t="shared" si="43"/>
-        <v>79.191899431941238</v>
-      </c>
-      <c r="AN15" s="3">
-        <f t="shared" si="43"/>
-        <v>113.30862858596021</v>
-      </c>
-      <c r="AO15" s="3">
-        <f t="shared" si="43"/>
-        <v>141.9146074807872</v>
-      </c>
-      <c r="AP15" s="3">
-        <f t="shared" ref="AP15" si="44">AP12-AP13-AP14</f>
-        <v>164.09875149187224</v>
-      </c>
-      <c r="AQ15" s="3">
-        <f t="shared" ref="AQ15:AT15" si="45">AQ12-AQ13-AQ14</f>
-        <v>186.98449894817759</v>
-      </c>
-      <c r="AR15" s="3">
-        <f t="shared" si="45"/>
-        <v>210.60087472027169</v>
-      </c>
-      <c r="AS15" s="3">
-        <f t="shared" si="45"/>
-        <v>234.97765227593675</v>
-      </c>
-      <c r="AT15" s="3">
-        <f t="shared" si="45"/>
-        <v>260.14538118659522</v>
-      </c>
-      <c r="AU15" s="3">
-        <f>AT15*(1+$AW$18)</f>
-        <v>257.54392737472926</v>
-      </c>
-      <c r="AV15" s="3">
-        <f t="shared" ref="AV15:DG15" si="46">AU15*(1+$AW$18)</f>
-        <v>254.96848810098197</v>
-      </c>
-      <c r="AW15" s="3">
-        <f t="shared" si="46"/>
-        <v>252.41880321997215</v>
-      </c>
-      <c r="AX15" s="3">
-        <f t="shared" si="46"/>
-        <v>249.89461518777242</v>
-      </c>
-      <c r="AY15" s="3">
-        <f t="shared" si="46"/>
-        <v>247.39566903589468</v>
-      </c>
-      <c r="AZ15" s="3">
-        <f t="shared" si="46"/>
-        <v>244.92171234553572</v>
-      </c>
-      <c r="BA15" s="3">
-        <f t="shared" si="46"/>
-        <v>242.47249522208037</v>
-      </c>
-      <c r="BB15" s="3">
-        <f t="shared" si="46"/>
-        <v>240.04777026985957</v>
-      </c>
-      <c r="BC15" s="3">
-        <f t="shared" si="46"/>
-        <v>237.64729256716097</v>
-      </c>
-      <c r="BD15" s="3">
-        <f t="shared" si="46"/>
-        <v>235.27081964148937</v>
-      </c>
-      <c r="BE15" s="3">
-        <f t="shared" si="46"/>
-        <v>232.91811144507446</v>
-      </c>
-      <c r="BF15" s="3">
-        <f t="shared" si="46"/>
-        <v>230.58893033062373</v>
-      </c>
-      <c r="BG15" s="3">
-        <f t="shared" si="46"/>
-        <v>228.28304102731749</v>
-      </c>
-      <c r="BH15" s="3">
-        <f t="shared" si="46"/>
-        <v>226.00021061704433</v>
-      </c>
-      <c r="BI15" s="3">
-        <f t="shared" si="46"/>
-        <v>223.74020851087388</v>
-      </c>
-      <c r="BJ15" s="3">
-        <f t="shared" si="46"/>
-        <v>221.50280642576513</v>
-      </c>
-      <c r="BK15" s="3">
-        <f t="shared" si="46"/>
-        <v>219.28777836150746</v>
-      </c>
-      <c r="BL15" s="3">
-        <f t="shared" si="46"/>
-        <v>217.09490057789239</v>
-      </c>
-      <c r="BM15" s="3">
-        <f t="shared" si="46"/>
-        <v>214.92395157211345</v>
-      </c>
-      <c r="BN15" s="3">
-        <f t="shared" si="46"/>
-        <v>212.7747120563923</v>
-      </c>
-      <c r="BO15" s="3">
-        <f t="shared" si="46"/>
-        <v>210.64696493582838</v>
-      </c>
-      <c r="BP15" s="3">
-        <f t="shared" si="46"/>
-        <v>208.5404952864701</v>
-      </c>
-      <c r="BQ15" s="3">
-        <f t="shared" si="46"/>
-        <v>206.4550903336054</v>
-      </c>
-      <c r="BR15" s="3">
-        <f t="shared" si="46"/>
-        <v>204.39053943026934</v>
-      </c>
-      <c r="BS15" s="3">
-        <f t="shared" si="46"/>
-        <v>202.34663403596664</v>
-      </c>
-      <c r="BT15" s="3">
-        <f t="shared" si="46"/>
-        <v>200.32316769560697</v>
-      </c>
-      <c r="BU15" s="3">
-        <f t="shared" si="46"/>
-        <v>198.31993601865091</v>
-      </c>
-      <c r="BV15" s="3">
-        <f t="shared" si="46"/>
-        <v>196.33673665846439</v>
-      </c>
-      <c r="BW15" s="3">
-        <f t="shared" si="46"/>
-        <v>194.37336929187975</v>
-      </c>
-      <c r="BX15" s="3">
-        <f t="shared" si="46"/>
-        <v>192.42963559896094</v>
-      </c>
-      <c r="BY15" s="3">
-        <f t="shared" si="46"/>
-        <v>190.50533924297133</v>
-      </c>
-      <c r="BZ15" s="3">
-        <f t="shared" si="46"/>
-        <v>188.60028585054161</v>
-      </c>
-      <c r="CA15" s="3">
-        <f t="shared" si="46"/>
-        <v>186.7142829920362</v>
-      </c>
-      <c r="CB15" s="3">
-        <f t="shared" si="46"/>
-        <v>184.84714016211583</v>
-      </c>
-      <c r="CC15" s="3">
-        <f t="shared" si="46"/>
-        <v>182.99866876049467</v>
-      </c>
-      <c r="CD15" s="3">
-        <f t="shared" si="46"/>
-        <v>181.16868207288971</v>
-      </c>
-      <c r="CE15" s="3">
-        <f t="shared" si="46"/>
-        <v>179.3569952521608</v>
-      </c>
-      <c r="CF15" s="3">
-        <f t="shared" si="46"/>
-        <v>177.56342529963919</v>
-      </c>
-      <c r="CG15" s="3">
-        <f t="shared" si="46"/>
-        <v>175.78779104664281</v>
-      </c>
-      <c r="CH15" s="3">
-        <f t="shared" si="46"/>
-        <v>174.02991313617639</v>
-      </c>
-      <c r="CI15" s="3">
-        <f t="shared" si="46"/>
-        <v>172.28961400481464</v>
-      </c>
-      <c r="CJ15" s="3">
-        <f t="shared" si="46"/>
-        <v>170.5667178647665</v>
-      </c>
-      <c r="CK15" s="3">
-        <f t="shared" si="46"/>
-        <v>168.86105068611883</v>
-      </c>
-      <c r="CL15" s="3">
-        <f t="shared" si="46"/>
-        <v>167.17244017925765</v>
-      </c>
-      <c r="CM15" s="3">
-        <f t="shared" si="46"/>
-        <v>165.50071577746508</v>
-      </c>
-      <c r="CN15" s="3">
-        <f t="shared" si="46"/>
-        <v>163.84570861969041</v>
-      </c>
-      <c r="CO15" s="3">
-        <f t="shared" si="46"/>
-        <v>162.20725153349352</v>
-      </c>
-      <c r="CP15" s="3">
-        <f t="shared" si="46"/>
-        <v>160.58517901815858</v>
-      </c>
-      <c r="CQ15" s="3">
-        <f t="shared" si="46"/>
-        <v>158.979327227977</v>
-      </c>
-      <c r="CR15" s="3">
-        <f t="shared" si="46"/>
-        <v>157.38953395569723</v>
-      </c>
-      <c r="CS15" s="3">
-        <f t="shared" si="46"/>
-        <v>155.81563861614026</v>
-      </c>
-      <c r="CT15" s="3">
-        <f t="shared" si="46"/>
-        <v>154.25748222997885</v>
-      </c>
-      <c r="CU15" s="3">
-        <f t="shared" si="46"/>
-        <v>152.71490740767905</v>
-      </c>
-      <c r="CV15" s="3">
-        <f t="shared" si="46"/>
-        <v>151.18775833360226</v>
-      </c>
-      <c r="CW15" s="3">
-        <f t="shared" si="46"/>
-        <v>149.67588075026623</v>
-      </c>
-      <c r="CX15" s="3">
-        <f t="shared" si="46"/>
-        <v>148.17912194276357</v>
-      </c>
-      <c r="CY15" s="3">
-        <f t="shared" si="46"/>
-        <v>146.69733072333594</v>
-      </c>
-      <c r="CZ15" s="3">
-        <f t="shared" si="46"/>
-        <v>145.23035741610258</v>
-      </c>
-      <c r="DA15" s="3">
-        <f t="shared" si="46"/>
-        <v>143.77805384194156</v>
-      </c>
-      <c r="DB15" s="3">
-        <f t="shared" si="46"/>
-        <v>142.34027330352214</v>
-      </c>
-      <c r="DC15" s="3">
-        <f t="shared" si="46"/>
-        <v>140.91687057048691</v>
-      </c>
-      <c r="DD15" s="3">
-        <f t="shared" si="46"/>
-        <v>139.50770186478204</v>
-      </c>
-      <c r="DE15" s="3">
-        <f t="shared" si="46"/>
-        <v>138.11262484613422</v>
-      </c>
-      <c r="DF15" s="3">
-        <f t="shared" si="46"/>
-        <v>136.73149859767287</v>
-      </c>
-      <c r="DG15" s="3">
-        <f t="shared" si="46"/>
-        <v>135.36418361169615</v>
-      </c>
-      <c r="DH15" s="3">
-        <f t="shared" ref="DH15:DL15" si="47">DG15*(1+$AW$18)</f>
-        <v>134.01054177557918</v>
-      </c>
-      <c r="DI15" s="3">
-        <f t="shared" si="47"/>
-        <v>132.67043635782341</v>
-      </c>
-      <c r="DJ15" s="3">
-        <f t="shared" si="47"/>
-        <v>131.34373199424516</v>
-      </c>
-      <c r="DK15" s="3">
-        <f t="shared" si="47"/>
-        <v>130.0302946743027</v>
-      </c>
-      <c r="DL15" s="3">
-        <f t="shared" si="47"/>
-        <v>128.72999172755968</v>
+        <v>180.67346810440421</v>
       </c>
     </row>
-    <row r="16" spans="3:116" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:120" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
@@ -3063,32 +3150,24 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
-      <c r="AC16" s="1">
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
+      <c r="AD16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AG16" s="1">
         <v>228</v>
       </c>
-      <c r="AD16" s="1">
+      <c r="AH16" s="1">
         <v>228</v>
       </c>
-      <c r="AE16" s="1">
+      <c r="AI16" s="1">
         <v>115</v>
       </c>
-      <c r="AF16" s="1">
+      <c r="AJ16" s="1">
         <v>115</v>
       </c>
-      <c r="AG16" s="1">
+      <c r="AK16" s="1">
         <v>115</v>
-      </c>
-      <c r="AH16" s="1">
-        <v>822.6</v>
-      </c>
-      <c r="AI16" s="1">
-        <v>822.6</v>
-      </c>
-      <c r="AJ16" s="1">
-        <v>822.6</v>
-      </c>
-      <c r="AK16" s="1">
-        <v>822.6</v>
       </c>
       <c r="AL16" s="1">
         <v>822.6</v>
@@ -3097,149 +3176,161 @@
         <v>822.6</v>
       </c>
       <c r="AN16" s="1">
-        <v>822.6</v>
+        <v>955.5</v>
       </c>
       <c r="AO16" s="1">
-        <v>822.6</v>
+        <v>955.5</v>
       </c>
       <c r="AP16" s="1">
-        <v>822.6</v>
+        <v>955.5</v>
       </c>
       <c r="AQ16" s="1">
-        <v>822.6</v>
+        <v>955.5</v>
       </c>
       <c r="AR16" s="1">
-        <v>822.6</v>
+        <v>955.5</v>
       </c>
       <c r="AS16" s="1">
-        <v>822.6</v>
+        <v>955.5</v>
       </c>
       <c r="AT16" s="1">
-        <v>822.6</v>
+        <v>955.5</v>
+      </c>
+      <c r="AU16" s="1">
+        <v>955.5</v>
+      </c>
+      <c r="AV16" s="1">
+        <v>955.5</v>
+      </c>
+      <c r="AW16" s="1">
+        <v>955.5</v>
+      </c>
+      <c r="AX16" s="1">
+        <v>955.5</v>
       </c>
     </row>
-    <row r="17" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" ref="D17:K17" si="48">D15/D16</f>
+        <f t="shared" ref="D17:K17" si="44">D15/D16</f>
         <v>-6.096491228070177E-2</v>
       </c>
       <c r="E17" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>-0.21535087719298227</v>
       </c>
       <c r="F17" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>-4.4298245614035087E-2</v>
       </c>
       <c r="G17" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>-0.1758771929824566</v>
       </c>
       <c r="H17" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>-0.32894736842105265</v>
       </c>
       <c r="I17" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>-6.0910087719298248E-2</v>
       </c>
       <c r="J17" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>-3.7280701754385956E-2</v>
       </c>
       <c r="K17" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>-1.2182608695652175</v>
       </c>
       <c r="L17" s="2">
-        <f t="shared" ref="L17" si="49">L15/L16</f>
+        <f t="shared" ref="L17" si="45">L15/L16</f>
         <v>-0.3704347826086955</v>
       </c>
-      <c r="AC17" s="2">
-        <f t="shared" ref="AC17" si="50">AC15/AC16</f>
+      <c r="AG17" s="2">
+        <f t="shared" ref="AG17" si="46">AG15/AG16</f>
         <v>-0.27500000000000019</v>
       </c>
-      <c r="AD17" s="2">
-        <f>AD15/AD16</f>
+      <c r="AH17" s="2">
+        <f>AH15/AH16</f>
         <v>-0.49649122807017571</v>
       </c>
-      <c r="AE17" s="2">
-        <f>AE15/AE16</f>
+      <c r="AI17" s="2">
+        <f>AI15/AI16</f>
         <v>-3.6452173913043486</v>
       </c>
-      <c r="AF17" s="2">
-        <f t="shared" ref="AF17:AO17" si="51">AF15/AF16</f>
+      <c r="AJ17" s="2">
+        <f t="shared" ref="AJ17:AS17" si="47">AJ15/AJ16</f>
         <v>-1.6660869565217395</v>
       </c>
-      <c r="AG17" s="2">
-        <f t="shared" si="51"/>
+      <c r="AK17" s="2">
+        <f t="shared" si="47"/>
         <v>-4.5965217391304343</v>
       </c>
-      <c r="AH17" s="2">
-        <f t="shared" si="51"/>
+      <c r="AL17" s="2">
+        <f t="shared" si="47"/>
         <v>-0.27729151470945795</v>
       </c>
-      <c r="AI17" s="2">
-        <f t="shared" si="51"/>
-        <v>-0.29132579625577437</v>
-      </c>
-      <c r="AJ17" s="2">
-        <f t="shared" si="51"/>
-        <v>-0.16698660685630931</v>
-      </c>
-      <c r="AK17" s="2">
-        <f t="shared" si="51"/>
-        <v>-5.5232012110868062E-2</v>
-      </c>
-      <c r="AL17" s="2">
-        <f t="shared" si="51"/>
-        <v>3.4546053283856869E-2</v>
-      </c>
       <c r="AM17" s="2">
-        <f t="shared" si="51"/>
-        <v>9.6270240009653826E-2</v>
+        <f t="shared" si="47"/>
+        <v>-0.39326525650376837</v>
       </c>
       <c r="AN17" s="2">
-        <f t="shared" si="51"/>
-        <v>0.13774450350833967</v>
+        <f t="shared" si="47"/>
+        <v>-0.17734232548403975</v>
       </c>
       <c r="AO17" s="2">
-        <f t="shared" si="51"/>
-        <v>0.17251958118257621</v>
+        <f t="shared" si="47"/>
+        <v>-2.575092070748285E-2</v>
       </c>
       <c r="AP17" s="2">
-        <f t="shared" ref="AP17" si="52">AP15/AP16</f>
-        <v>0.19948790601978147</v>
+        <f t="shared" si="47"/>
+        <v>8.7763879252864344E-2</v>
       </c>
       <c r="AQ17" s="2">
-        <f t="shared" ref="AQ17:AT17" si="53">AQ15/AQ16</f>
-        <v>0.22730914046702844</v>
+        <f t="shared" si="47"/>
+        <v>0.17311378379604478</v>
       </c>
       <c r="AR17" s="2">
-        <f t="shared" si="53"/>
-        <v>0.2560185688308676</v>
+        <f t="shared" si="47"/>
+        <v>0.23094350054381782</v>
       </c>
       <c r="AS17" s="2">
-        <f t="shared" si="53"/>
-        <v>0.28565238545579474</v>
+        <f t="shared" si="47"/>
+        <v>0.26109668628032667</v>
       </c>
       <c r="AT17" s="2">
-        <f t="shared" si="53"/>
-        <v>0.31624772816264918</v>
+        <f t="shared" ref="AT17" si="48">AT15/AT16</f>
+        <v>0.28398711353189732</v>
+      </c>
+      <c r="AU17" s="2">
+        <f t="shared" ref="AU17:AX17" si="49">AU15/AU16</f>
+        <v>0.30750598348873714</v>
+      </c>
+      <c r="AV17" s="2">
+        <f t="shared" si="49"/>
+        <v>0.33168163497922437</v>
+      </c>
+      <c r="AW17" s="2">
+        <f t="shared" si="49"/>
+        <v>0.35654312612568906</v>
+      </c>
+      <c r="AX17" s="2">
+        <f t="shared" si="49"/>
+        <v>0.3821202629148428</v>
       </c>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="AV18" t="s">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AZ18" t="s">
         <v>38</v>
       </c>
-      <c r="AW18" s="7">
+      <c r="BA18" s="7">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="19" spans="1:49" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:53" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19" s="4" t="s">
@@ -3250,163 +3341,173 @@
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
       <c r="H19" s="14">
-        <f t="shared" ref="H19:O19" si="54">H3/D3-1</f>
+        <f t="shared" ref="H19:O19" si="50">H3/D3-1</f>
         <v>-0.59897959183673466</v>
       </c>
       <c r="I19" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>-0.68072003789673141</v>
       </c>
       <c r="J19" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>-0.50419832067173131</v>
       </c>
       <c r="K19" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>4.9985298441637127E-3</v>
       </c>
       <c r="L19" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>1.8549618320610688</v>
       </c>
       <c r="M19" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>3.0712166172106814</v>
       </c>
       <c r="N19" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>0.91612903225806441</v>
       </c>
       <c r="O19" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>0.53130485664131077</v>
       </c>
       <c r="P19" s="14">
-        <f t="shared" ref="P19" si="55">P3/L3-1</f>
+        <f t="shared" ref="P19" si="51">P3/L3-1</f>
         <v>3.6987522281639817E-2</v>
       </c>
       <c r="Q19" s="14">
-        <f t="shared" ref="Q19" si="56">Q3/M3-1</f>
+        <f t="shared" ref="Q19" si="52">Q3/M3-1</f>
         <v>0.12609329446064144</v>
       </c>
       <c r="R19" s="14">
-        <f t="shared" ref="R19" si="57">R3/N3-1</f>
+        <f t="shared" ref="R19" si="53">R3/N3-1</f>
         <v>0.32786195286195285</v>
       </c>
       <c r="S19" s="14">
-        <f t="shared" ref="S19" si="58">S3/O3-1</f>
+        <f t="shared" ref="S19" si="54">S3/O3-1</f>
         <v>1.7195261750095892E-3</v>
       </c>
       <c r="T19" s="14">
-        <f t="shared" ref="T19" si="59">T3/P3-1</f>
+        <f t="shared" ref="T19" si="55">T3/P3-1</f>
         <v>0.27159432746024925</v>
       </c>
       <c r="U19" s="14">
-        <f t="shared" ref="U19" si="60">U3/Q3-1</f>
+        <f t="shared" ref="U19" si="56">U3/Q3-1</f>
         <v>0.2346278317152104</v>
       </c>
       <c r="V19" s="14">
-        <f t="shared" ref="V19" si="61">V3/R3-1</f>
+        <f t="shared" ref="V19" si="57">V3/R3-1</f>
         <v>0.14770206022187016</v>
       </c>
       <c r="W19" s="14">
-        <f t="shared" ref="W19" si="62">W3/S3-1</f>
+        <f t="shared" ref="W19" si="58">W3/S3-1</f>
         <v>0.13160404348655352</v>
       </c>
       <c r="X19" s="14">
-        <f t="shared" ref="X19" si="63">X3/T3-1</f>
+        <f t="shared" ref="X19" si="59">X3/T3-1</f>
         <v>-9.5302467049678929E-2</v>
       </c>
       <c r="Y19" s="14">
-        <f t="shared" ref="Y19" si="64">Y3/U3-1</f>
+        <f t="shared" ref="Y19" si="60">Y3/U3-1</f>
         <v>-0.12110091743119267</v>
       </c>
       <c r="Z19" s="14">
-        <f t="shared" ref="Z19" si="65">Z3/V3-1</f>
+        <f t="shared" ref="Z19" si="61">Z3/V3-1</f>
         <v>8.1469207401270394E-2</v>
       </c>
       <c r="AA19" s="14">
-        <f t="shared" ref="AA19" si="66">AA3/W3-1</f>
+        <f t="shared" ref="AA19" si="62">AA3/W3-1</f>
         <v>-0.15000000000000002</v>
       </c>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="14"/>
-      <c r="AD19" s="14">
-        <f t="shared" ref="AD19:AO19" si="67">AD3/AC3-1</f>
+      <c r="AB19" s="14">
+        <f t="shared" ref="AB19" si="63">AB3/X3-1</f>
+        <v>-0.12626073963391848</v>
+      </c>
+      <c r="AC19" s="14">
+        <f t="shared" ref="AC19" si="64">AC3/Y3-1</f>
+        <v>-0.34237995824634671</v>
+      </c>
+      <c r="AD19" s="14"/>
+      <c r="AE19" s="14"/>
+      <c r="AF19" s="4"/>
+      <c r="AG19" s="14"/>
+      <c r="AH19" s="14">
+        <f t="shared" ref="AH19:AS19" si="65">AH3/AG3-1</f>
         <v>-9.0469676242590058E-2</v>
       </c>
-      <c r="AE19" s="14">
-        <f t="shared" si="67"/>
+      <c r="AI19" s="14">
+        <f t="shared" si="65"/>
         <v>-0.38654366790333905</v>
       </c>
-      <c r="AF19" s="14">
-        <f t="shared" si="67"/>
+      <c r="AJ19" s="14">
+        <f t="shared" si="65"/>
         <v>0.7902909447531874</v>
       </c>
-      <c r="AG19" s="14">
-        <f t="shared" si="67"/>
+      <c r="AK19" s="14">
+        <f t="shared" si="65"/>
         <v>0.26129827444535758</v>
       </c>
-      <c r="AH19" s="14">
-        <f t="shared" si="67"/>
+      <c r="AL19" s="14">
+        <f t="shared" si="65"/>
         <v>0.18190372783206654</v>
       </c>
-      <c r="AI19" s="14">
-        <f t="shared" si="67"/>
-        <v>-8.2003307202351827E-2</v>
-      </c>
-      <c r="AJ19" s="14">
-        <f t="shared" si="67"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AK19" s="14">
-        <f t="shared" si="67"/>
-        <v>0.1399999999999999</v>
-      </c>
-      <c r="AL19" s="14">
-        <f t="shared" si="67"/>
+      <c r="AM19" s="14">
+        <f t="shared" si="65"/>
+        <v>-2.9948554630083168E-2</v>
+      </c>
+      <c r="AN19" s="14">
+        <f t="shared" si="65"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AO19" s="14">
+        <f t="shared" si="65"/>
+        <v>0.25</v>
+      </c>
+      <c r="AP19" s="14">
+        <f t="shared" si="65"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AQ19" s="14">
+        <f t="shared" si="65"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AM19" s="14">
-        <f t="shared" si="67"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AN19" s="14">
-        <f t="shared" si="67"/>
+      <c r="AR19" s="14">
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AO19" s="14">
-        <f t="shared" si="67"/>
+      <c r="AS19" s="14">
+        <f t="shared" si="65"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AP19" s="14">
-        <f t="shared" ref="AP19" si="68">AP3/AO3-1</f>
+      <c r="AT19" s="14">
+        <f t="shared" ref="AT19" si="66">AT3/AS3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AQ19" s="14">
-        <f t="shared" ref="AQ19" si="69">AQ3/AP3-1</f>
+      <c r="AU19" s="14">
+        <f t="shared" ref="AU19" si="67">AU3/AT3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AR19" s="14">
-        <f t="shared" ref="AR19" si="70">AR3/AQ3-1</f>
+      <c r="AV19" s="14">
+        <f t="shared" ref="AV19" si="68">AV3/AU3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AS19" s="14">
-        <f t="shared" ref="AS19" si="71">AS3/AR3-1</f>
+      <c r="AW19" s="14">
+        <f t="shared" ref="AW19" si="69">AW3/AV3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AT19" s="14">
-        <f t="shared" ref="AT19" si="72">AT3/AS3-1</f>
+      <c r="AX19" s="14">
+        <f t="shared" ref="AX19" si="70">AX3/AW3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AV19" s="5" t="s">
+      <c r="AZ19" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AW19" s="7">
-        <v>0.08</v>
+      <c r="BA19" s="7">
+        <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="1:49" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:53" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20" s="4" t="s">
@@ -3417,179 +3518,189 @@
         <v>0.42142857142857137</v>
       </c>
       <c r="E20" s="14">
-        <f t="shared" ref="E20:K20" si="73">E5/E3</f>
+        <f t="shared" ref="E20:K20" si="71">E5/E3</f>
         <v>0.30933207010895325</v>
       </c>
       <c r="F20" s="14">
+        <f t="shared" si="71"/>
+        <v>0.38344662135145946</v>
+      </c>
+      <c r="G20" s="14">
+        <f t="shared" si="71"/>
+        <v>0.32578653337253721</v>
+      </c>
+      <c r="H20" s="14">
+        <f t="shared" si="71"/>
+        <v>5.2162849872773469E-2</v>
+      </c>
+      <c r="I20" s="14">
+        <f t="shared" si="71"/>
+        <v>-0.10237388724035616</v>
+      </c>
+      <c r="J20" s="14">
+        <f t="shared" si="71"/>
+        <v>0.13629032258064522</v>
+      </c>
+      <c r="K20" s="14">
+        <f t="shared" si="71"/>
+        <v>0.28379169104739599</v>
+      </c>
+      <c r="L20" s="14">
+        <f t="shared" ref="L20:O20" si="72">L5/L3</f>
+        <v>0.28208556149732622</v>
+      </c>
+      <c r="M20" s="14">
+        <f t="shared" si="72"/>
+        <v>0.29154518950437308</v>
+      </c>
+      <c r="N20" s="14">
+        <f t="shared" si="72"/>
+        <v>0.33080808080808077</v>
+      </c>
+      <c r="O20" s="14">
+        <f t="shared" si="72"/>
+        <v>0.31257164692395867</v>
+      </c>
+      <c r="P20" s="14">
+        <f t="shared" ref="P20:AA20" si="73">P5/P3</f>
+        <v>0.36097980232058446</v>
+      </c>
+      <c r="Q20" s="14">
         <f t="shared" si="73"/>
-        <v>0.38344662135145946</v>
-      </c>
-      <c r="G20" s="14">
+        <v>0.33689320388349514</v>
+      </c>
+      <c r="R20" s="14">
         <f t="shared" si="73"/>
-        <v>0.32578653337253721</v>
-      </c>
-      <c r="H20" s="14">
+        <v>0.31093502377179078</v>
+      </c>
+      <c r="S20" s="14">
         <f t="shared" si="73"/>
-        <v>5.2162849872773469E-2</v>
-      </c>
-      <c r="I20" s="14">
+        <v>0.31375166889185574</v>
+      </c>
+      <c r="T20" s="14">
         <f t="shared" si="73"/>
-        <v>-0.10237388724035616</v>
-      </c>
-      <c r="J20" s="14">
+        <v>0.34437309901993912</v>
+      </c>
+      <c r="U20" s="14">
         <f t="shared" si="73"/>
-        <v>0.13629032258064522</v>
-      </c>
-      <c r="K20" s="14">
+        <v>0.35150720838794242</v>
+      </c>
+      <c r="V20" s="14">
         <f t="shared" si="73"/>
-        <v>0.28379169104739599</v>
-      </c>
-      <c r="L20" s="14">
-        <f t="shared" ref="L20:O20" si="74">L5/L3</f>
-        <v>0.28208556149732622</v>
-      </c>
-      <c r="M20" s="14">
+        <v>0.37144435238884294</v>
+      </c>
+      <c r="W20" s="14">
+        <f t="shared" si="73"/>
+        <v>0.45238496544749707</v>
+      </c>
+      <c r="X20" s="14">
+        <f t="shared" si="73"/>
+        <v>0.37243182667164726</v>
+      </c>
+      <c r="Y20" s="14">
+        <f t="shared" si="73"/>
+        <v>0.39725618848792132</v>
+      </c>
+      <c r="Z20" s="14">
+        <f t="shared" si="73"/>
+        <v>0.36772216547497449</v>
+      </c>
+      <c r="AA20" s="14">
+        <f t="shared" si="73"/>
+        <v>0.45</v>
+      </c>
+      <c r="AB20" s="14">
+        <f t="shared" ref="AB20:AC20" si="74">AB5/AB3</f>
+        <v>0.27875160324925186</v>
+      </c>
+      <c r="AC20" s="14">
         <f t="shared" si="74"/>
-        <v>0.29154518950437308</v>
-      </c>
-      <c r="N20" s="14">
-        <f t="shared" si="74"/>
-        <v>0.33080808080808077</v>
-      </c>
-      <c r="O20" s="14">
-        <f t="shared" si="74"/>
-        <v>0.31257164692395867</v>
-      </c>
-      <c r="P20" s="14">
-        <f t="shared" ref="P20:AA20" si="75">P5/P3</f>
-        <v>0.36097980232058446</v>
-      </c>
-      <c r="Q20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.33689320388349514</v>
-      </c>
-      <c r="R20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.31093502377179078</v>
-      </c>
-      <c r="S20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.31375166889185574</v>
-      </c>
-      <c r="T20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.34437309901993912</v>
-      </c>
-      <c r="U20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.35150720838794242</v>
-      </c>
-      <c r="V20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.37144435238884294</v>
-      </c>
-      <c r="W20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.45238496544749707</v>
-      </c>
-      <c r="X20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.37243182667164726</v>
-      </c>
-      <c r="Y20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.39725618848792132</v>
-      </c>
-      <c r="Z20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.36772216547497449</v>
-      </c>
-      <c r="AA20" s="14">
-        <f t="shared" si="75"/>
-        <v>0.45</v>
-      </c>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="14">
-        <f t="shared" ref="AC20" si="76">AC5/AC3</f>
+        <v>0.2784580498866211</v>
+      </c>
+      <c r="AD20" s="14"/>
+      <c r="AE20" s="14"/>
+      <c r="AF20" s="11"/>
+      <c r="AG20" s="14">
+        <f t="shared" ref="AG20" si="75">AG5/AG3</f>
         <v>0.39744642042863654</v>
       </c>
-      <c r="AD20" s="14">
-        <f t="shared" ref="AD20:AO20" si="77">AD5/AD3</f>
+      <c r="AH20" s="14">
+        <f t="shared" ref="AH20:AS20" si="76">AH5/AH3</f>
         <v>0.35556001203248766</v>
       </c>
-      <c r="AE20" s="14">
-        <f t="shared" si="77"/>
+      <c r="AI20" s="14">
+        <f t="shared" si="76"/>
         <v>0.18159529257927415</v>
       </c>
-      <c r="AF20" s="14">
-        <f t="shared" si="77"/>
+      <c r="AJ20" s="14">
+        <f t="shared" si="76"/>
         <v>0.31379530722176568</v>
       </c>
-      <c r="AG20" s="14">
-        <f t="shared" si="77"/>
+      <c r="AK20" s="14">
+        <f t="shared" si="76"/>
         <v>0.32623959464350349</v>
       </c>
-      <c r="AH20" s="14">
-        <f t="shared" si="77"/>
+      <c r="AL20" s="14">
+        <f t="shared" si="76"/>
         <v>0.3914747672709456</v>
       </c>
-      <c r="AI20" s="14">
-        <f t="shared" si="77"/>
-        <v>0.39</v>
-      </c>
-      <c r="AJ20" s="14">
-        <f t="shared" si="77"/>
+      <c r="AM20" s="14">
+        <f t="shared" si="76"/>
+        <v>0.36864701054359494</v>
+      </c>
+      <c r="AN20" s="14">
+        <f t="shared" si="76"/>
+        <v>0.37</v>
+      </c>
+      <c r="AO20" s="14">
+        <f t="shared" si="76"/>
+        <v>0.4</v>
+      </c>
+      <c r="AP20" s="14">
+        <f t="shared" si="76"/>
         <v>0.42</v>
       </c>
-      <c r="AK20" s="14">
-        <f t="shared" si="77"/>
-        <v>0.43</v>
-      </c>
-      <c r="AL20" s="14">
-        <f t="shared" si="77"/>
+      <c r="AQ20" s="14">
+        <f t="shared" si="76"/>
+        <v>0.42999999999999994</v>
+      </c>
+      <c r="AR20" s="14">
+        <f t="shared" si="76"/>
         <v>0.44</v>
       </c>
-      <c r="AM20" s="14">
-        <f t="shared" si="77"/>
+      <c r="AS20" s="14">
+        <f t="shared" si="76"/>
+        <v>0.44</v>
+      </c>
+      <c r="AT20" s="14">
+        <f t="shared" ref="AT20" si="77">AT5/AT3</f>
         <v>0.44000000000000006</v>
       </c>
-      <c r="AN20" s="14">
-        <f t="shared" si="77"/>
-        <v>0.44000000000000006</v>
-      </c>
-      <c r="AO20" s="14">
-        <f t="shared" si="77"/>
+      <c r="AU20" s="14">
+        <f t="shared" ref="AU20:AX20" si="78">AU5/AU3</f>
         <v>0.44</v>
       </c>
-      <c r="AP20" s="14">
-        <f t="shared" ref="AP20" si="78">AP5/AP3</f>
+      <c r="AV20" s="14">
+        <f t="shared" si="78"/>
         <v>0.44</v>
       </c>
-      <c r="AQ20" s="14">
-        <f t="shared" ref="AQ20:AT20" si="79">AQ5/AQ3</f>
+      <c r="AW20" s="14">
+        <f t="shared" si="78"/>
         <v>0.44</v>
       </c>
-      <c r="AR20" s="14">
-        <f t="shared" si="79"/>
+      <c r="AX20" s="14">
+        <f t="shared" si="78"/>
         <v>0.44</v>
       </c>
-      <c r="AS20" s="14">
-        <f t="shared" si="79"/>
-        <v>0.44</v>
-      </c>
-      <c r="AT20" s="14">
-        <f t="shared" si="79"/>
-        <v>0.44</v>
-      </c>
-      <c r="AV20" s="5" t="s">
+      <c r="AZ20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AW20" s="1">
-        <f>NPV(AW19,AI15:DL15)</f>
-        <v>1470.9056176601621</v>
+      <c r="BA20" s="1">
+        <f>NPV(BA19,AM15:DP15)</f>
+        <v>1615.4502718208068</v>
       </c>
     </row>
-    <row r="21" spans="1:49" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:53" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21" t="s">
@@ -3600,47 +3711,47 @@
         <v>-1.6326530612244913E-2</v>
       </c>
       <c r="E21" s="7">
-        <f t="shared" ref="E21:I21" si="80">E8/E3</f>
+        <f t="shared" ref="E21:I21" si="79">E8/E3</f>
         <v>-0.16342965419232569</v>
       </c>
       <c r="F21" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>4.1983206717313079E-2</v>
       </c>
       <c r="G21" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>-2.7932960893855049E-2</v>
       </c>
       <c r="H21" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>-0.96437659033078904</v>
       </c>
       <c r="I21" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>-1.2388724035608307</v>
       </c>
       <c r="J21" s="7">
-        <f t="shared" ref="J21" si="81">J8/J3</f>
+        <f t="shared" ref="J21" si="80">J8/J3</f>
         <v>-0.56209677419354831</v>
       </c>
       <c r="K21" s="7">
-        <f t="shared" ref="K21:O21" si="82">K8/K3</f>
+        <f t="shared" ref="K21:O21" si="81">K8/K3</f>
         <v>-0.2747220596840258</v>
       </c>
       <c r="L21" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>-6.8181818181818107E-2</v>
       </c>
       <c r="M21" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="N21" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="O21" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="P21" s="7"/>
@@ -3651,91 +3762,107 @@
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
+      <c r="X21" s="7">
+        <f t="shared" ref="X21:Y21" si="82">X8/X3</f>
+        <v>-0.21927530818079943</v>
+      </c>
+      <c r="Y21" s="7">
+        <f t="shared" si="82"/>
+        <v>-0.63644497464956762</v>
+      </c>
       <c r="Z21" s="7"/>
       <c r="AA21" s="7"/>
+      <c r="AB21" s="7">
+        <f t="shared" ref="AB21" si="83">AB8/AB3</f>
+        <v>-0.28772979905942708</v>
+      </c>
       <c r="AC21" s="7">
-        <f t="shared" ref="AC21" si="83">AC8/AC3</f>
+        <f t="shared" ref="AC21" si="84">AC8/AC3</f>
+        <v>-0.30566893424036279</v>
+      </c>
+      <c r="AD21" s="7"/>
+      <c r="AE21" s="7"/>
+      <c r="AG21" s="7">
+        <f t="shared" ref="AG21" si="85">AG8/AG3</f>
         <v>6.6393068855449114E-2</v>
       </c>
-      <c r="AD21" s="7">
-        <f t="shared" ref="AD21:AO21" si="84">AD8/AD3</f>
+      <c r="AH21" s="7">
+        <f t="shared" ref="AH21:AS21" si="86">AH8/AH3</f>
         <v>-3.6799358267321815E-2</v>
       </c>
-      <c r="AE21" s="7">
-        <f t="shared" si="84"/>
+      <c r="AI21" s="7">
+        <f t="shared" si="86"/>
         <v>-0.52778685845047424</v>
       </c>
-      <c r="AF21" s="7">
-        <f t="shared" si="84"/>
+      <c r="AJ21" s="7">
+        <f t="shared" si="86"/>
         <v>-6.9843878389482389E-2</v>
       </c>
-      <c r="AG21" s="7">
-        <f t="shared" si="84"/>
+      <c r="AK21" s="7">
+        <f t="shared" si="86"/>
         <v>-0.10264205573651825</v>
       </c>
-      <c r="AH21" s="7">
-        <f t="shared" si="84"/>
+      <c r="AL21" s="7">
+        <f t="shared" si="86"/>
         <v>-6.8103870651641418E-2</v>
       </c>
-      <c r="AI21" s="7">
-        <f t="shared" si="84"/>
-        <v>-0.12493019904530309</v>
-      </c>
-      <c r="AJ21" s="7">
-        <f t="shared" si="84"/>
-        <v>-3.4731754180551834E-2</v>
-      </c>
-      <c r="AK21" s="7">
-        <f t="shared" si="84"/>
-        <v>2.3661062048979924E-2</v>
-      </c>
-      <c r="AL21" s="7">
-        <f t="shared" si="84"/>
-        <v>6.0361520608608804E-2</v>
-      </c>
       <c r="AM21" s="7">
-        <f t="shared" si="84"/>
-        <v>7.9782533161754626E-2</v>
+        <f t="shared" si="86"/>
+        <v>-6.281962245091223E-2</v>
       </c>
       <c r="AN21" s="7">
-        <f t="shared" si="84"/>
-        <v>9.0457484279402034E-2</v>
+        <f t="shared" si="86"/>
+        <v>-1.5595791879084222E-2</v>
       </c>
       <c r="AO21" s="7">
-        <f t="shared" si="84"/>
-        <v>9.8232749155957685E-2</v>
+        <f t="shared" si="86"/>
+        <v>7.4064301156601967E-2</v>
       </c>
       <c r="AP21" s="7">
-        <f t="shared" ref="AP21" si="85">AP8/AP3</f>
-        <v>0.10331560839564789</v>
+        <f t="shared" si="86"/>
+        <v>0.11972715668808685</v>
       </c>
       <c r="AQ21" s="7">
-        <f t="shared" ref="AQ21:AT21" si="86">AQ8/AQ3</f>
-        <v>0.1082997713394217</v>
+        <f t="shared" si="86"/>
+        <v>0.14574699983804418</v>
       </c>
       <c r="AR21" s="7">
         <f t="shared" si="86"/>
-        <v>0.11318715442020959</v>
+        <v>0.16158279984267154</v>
       </c>
       <c r="AS21" s="7">
         <f t="shared" si="86"/>
-        <v>0.11797963685865213</v>
+        <v>0.16539851523031249</v>
       </c>
       <c r="AT21" s="7">
-        <f t="shared" si="86"/>
-        <v>0.12267906138566861</v>
-      </c>
-      <c r="AV21" s="5" t="s">
+        <f t="shared" ref="AT21" si="87">AT8/AT3</f>
+        <v>0.16728785003390179</v>
+      </c>
+      <c r="AU21" s="7">
+        <f t="shared" ref="AU21:AX21" si="88">AU8/AU3</f>
+        <v>0.16915884178114537</v>
+      </c>
+      <c r="AV21" s="7">
+        <f t="shared" si="88"/>
+        <v>0.17101166855996922</v>
+      </c>
+      <c r="AW21" s="7">
+        <f t="shared" si="88"/>
+        <v>0.17284650672928994</v>
+      </c>
+      <c r="AX21" s="7">
+        <f t="shared" si="88"/>
+        <v>0.17466353093580161</v>
+      </c>
+      <c r="AZ21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AW21" s="1">
+      <c r="BA21" s="1">
         <f>Main!D8</f>
-        <v>-974.2</v>
+        <v>-1169.8</v>
       </c>
     </row>
-    <row r="22" spans="1:49" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:53" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22" t="s">
@@ -3773,83 +3900,93 @@
         <f>Y6/(Y3+X3)</f>
         <v>0.1109452736318408</v>
       </c>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="14"/>
+      <c r="AA22" s="7">
+        <f>AA6/(AA3+Z3)</f>
+        <v>7.645899955910504E-2</v>
+      </c>
+      <c r="AB22" s="7"/>
+      <c r="AC22" s="7">
+        <f t="shared" ref="AC22" si="89">AC6/(AC3+AB3)</f>
+        <v>0.11905809859154931</v>
+      </c>
       <c r="AD22" s="7"/>
-      <c r="AE22" s="7">
-        <f>AE6/AE3</f>
+      <c r="AE22" s="7"/>
+      <c r="AF22" s="11"/>
+      <c r="AG22" s="14"/>
+      <c r="AH22" s="7"/>
+      <c r="AI22" s="7">
+        <f>AI6/AI3</f>
         <v>0.13010787839163127</v>
       </c>
-      <c r="AF22" s="7">
-        <f t="shared" ref="AF22:AT22" si="87">AF6/AF3</f>
+      <c r="AJ22" s="7">
+        <f t="shared" ref="AJ22:AX22" si="90">AJ6/AJ3</f>
         <v>7.7421710946772568E-2</v>
       </c>
-      <c r="AG22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AK22" s="7">
+        <f t="shared" si="90"/>
         <v>8.1795150199058989E-2</v>
       </c>
-      <c r="AH22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AL22" s="7">
+        <f t="shared" si="90"/>
         <v>8.8069573738363563E-2</v>
       </c>
-      <c r="AI22" s="7">
-        <f t="shared" si="87"/>
-        <v>0.09</v>
-      </c>
-      <c r="AJ22" s="7">
-        <f t="shared" si="87"/>
-        <v>0.09</v>
-      </c>
-      <c r="AK22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AM22" s="7">
+        <f t="shared" si="90"/>
+        <v>8.5485194772397244E-2</v>
+      </c>
+      <c r="AN22" s="7">
+        <f t="shared" si="90"/>
+        <v>8.9999999999999983E-2</v>
+      </c>
+      <c r="AO22" s="7">
+        <f t="shared" si="90"/>
         <v>0.08</v>
       </c>
-      <c r="AL22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AP22" s="7">
+        <f t="shared" si="90"/>
         <v>0.08</v>
       </c>
-      <c r="AM22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AQ22" s="7">
+        <f t="shared" si="90"/>
         <v>0.08</v>
       </c>
-      <c r="AN22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AR22" s="7">
+        <f t="shared" si="90"/>
         <v>0.08</v>
       </c>
-      <c r="AO22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AS22" s="7">
+        <f t="shared" si="90"/>
         <v>0.08</v>
       </c>
-      <c r="AP22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AT22" s="7">
+        <f t="shared" si="90"/>
         <v>0.08</v>
       </c>
-      <c r="AQ22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AU22" s="7">
+        <f t="shared" si="90"/>
         <v>0.08</v>
       </c>
-      <c r="AR22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AV22" s="7">
+        <f t="shared" si="90"/>
         <v>0.08</v>
       </c>
-      <c r="AS22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AW22" s="7">
+        <f t="shared" si="90"/>
         <v>0.08</v>
       </c>
-      <c r="AT22" s="7">
-        <f t="shared" si="87"/>
+      <c r="AX22" s="7">
+        <f t="shared" si="90"/>
         <v>0.08</v>
       </c>
-      <c r="AV22" s="5" t="s">
+      <c r="AZ22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AW22" s="1">
-        <f>AW20+AW21</f>
-        <v>496.70561766016203</v>
+      <c r="BA22" s="1">
+        <f>BA20+BA21</f>
+        <v>445.65027182080689</v>
       </c>
     </row>
-    <row r="23" spans="1:49" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:53" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23" t="s">
@@ -3908,117 +4045,127 @@
         <v>5.1391035548686181E-2</v>
       </c>
       <c r="Z23" s="7"/>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="14"/>
+      <c r="AA23" s="7">
+        <f>AA7/W7-1</f>
+        <v>-0.20672800460034513</v>
+      </c>
+      <c r="AB23" s="7"/>
+      <c r="AC23" s="7">
+        <f t="shared" ref="AC23" si="91">AC7/Y7-1</f>
+        <v>-0.23851525174568189</v>
+      </c>
       <c r="AD23" s="7"/>
       <c r="AE23" s="7"/>
-      <c r="AF23" s="7">
-        <f>AF7/AE7-1</f>
+      <c r="AF23" s="11"/>
+      <c r="AG23" s="14"/>
+      <c r="AH23" s="7"/>
+      <c r="AI23" s="7"/>
+      <c r="AJ23" s="7">
+        <f>AJ7/AI7-1</f>
         <v>-5.3611738148984234E-2</v>
       </c>
-      <c r="AG23" s="7">
-        <f t="shared" ref="AG23:AP23" si="88">AG7/AF7-1</f>
+      <c r="AK23" s="7">
+        <f t="shared" ref="AK23:AT23" si="92">AK7/AJ7-1</f>
         <v>0.4296362552176507</v>
       </c>
-      <c r="AH23" s="7">
-        <f t="shared" si="88"/>
+      <c r="AL23" s="7">
+        <f t="shared" si="92"/>
         <v>0.26506777893639222</v>
       </c>
-      <c r="AI23" s="7">
-        <f t="shared" si="88"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AJ23" s="7">
-        <f t="shared" si="88"/>
+      <c r="AM23" s="7">
+        <f t="shared" si="92"/>
+        <v>-9.6604022420046176E-2</v>
+      </c>
+      <c r="AN23" s="7">
+        <f t="shared" si="92"/>
+        <v>-0.12</v>
+      </c>
+      <c r="AO23" s="7">
+        <f t="shared" si="92"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AP23" s="7">
+        <f t="shared" si="92"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AK23" s="7">
-        <f t="shared" si="88"/>
+      <c r="AQ23" s="7">
+        <f t="shared" si="92"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AL23" s="7">
-        <f t="shared" si="88"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AM23" s="7">
-        <f t="shared" si="88"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AN23" s="7">
-        <f t="shared" si="88"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AO23" s="7">
-        <f t="shared" si="88"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AP23" s="7">
-        <f t="shared" si="88"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AQ23" s="7">
-        <f t="shared" ref="AQ23" si="89">AQ7/AP7-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AR23" s="7">
-        <f t="shared" ref="AR23" si="90">AR7/AQ7-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="92"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS23" s="7">
-        <f t="shared" ref="AS23" si="91">AS7/AR7-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="92"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT23" s="7">
-        <f t="shared" ref="AT23" si="92">AT7/AS7-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AV23" s="5" t="s">
+        <f t="shared" si="92"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AU23" s="7">
+        <f t="shared" ref="AU23" si="93">AU7/AT7-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AV23" s="7">
+        <f t="shared" ref="AV23" si="94">AV7/AU7-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AW23" s="7">
+        <f t="shared" ref="AW23" si="95">AW7/AV7-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AX23" s="7">
+        <f t="shared" ref="AX23" si="96">AX7/AW7-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AZ23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AW23" s="6">
-        <f>AW22/AO16</f>
-        <v>0.60382399423797961</v>
+      <c r="BA23" s="6">
+        <f>BA22/AS16</f>
+        <v>0.46640530802805535</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>31</v>
       </c>
       <c r="D24" s="7">
-        <f t="shared" ref="D24:L24" si="93">D13/D12</f>
+        <f t="shared" ref="D24:L24" si="97">D13/D12</f>
         <v>0.19653179190751441</v>
       </c>
       <c r="E24" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0.20162601626016274</v>
       </c>
       <c r="F24" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0.25185185185185183</v>
       </c>
       <c r="G24" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>-1.6083333333333196</v>
       </c>
       <c r="H24" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0.15254237288135591</v>
       </c>
       <c r="I24" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>-2.0109689213893958E-2</v>
       </c>
       <c r="J24" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0.15422885572139305</v>
       </c>
       <c r="K24" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0.17319848293299622</v>
       </c>
       <c r="L24" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>-9.4786729857819947E-3</v>
       </c>
       <c r="M24" s="7"/>
@@ -4036,88 +4183,92 @@
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
       <c r="AA24" s="7"/>
-      <c r="AB24" s="5"/>
-      <c r="AC24" s="7">
-        <f t="shared" ref="AC24:AO24" si="94">AC13/AC12</f>
+      <c r="AB24" s="7"/>
+      <c r="AC24" s="7"/>
+      <c r="AD24" s="7"/>
+      <c r="AE24" s="7"/>
+      <c r="AF24" s="5"/>
+      <c r="AG24" s="7">
+        <f t="shared" ref="AG24:AS24" si="98">AG13/AG12</f>
         <v>0.16275659824046909</v>
       </c>
-      <c r="AD24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AH24" s="7">
+        <f t="shared" si="98"/>
         <v>-9.5877277085332094E-4</v>
       </c>
-      <c r="AE24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AI24" s="7">
+        <f t="shared" si="98"/>
         <v>0.11931330472103004</v>
       </c>
-      <c r="AF24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AJ24" s="7">
+        <f t="shared" si="98"/>
         <v>0.11459307764265667</v>
       </c>
-      <c r="AG24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AK24" s="7">
+        <f t="shared" si="98"/>
         <v>-6.606060606060607E-2</v>
       </c>
-      <c r="AH24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AL24" s="7">
+        <f t="shared" si="98"/>
         <v>5.4211843202668863E-2</v>
       </c>
-      <c r="AI24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AM24" s="7">
+        <f t="shared" si="98"/>
+        <v>-0.11898996886890352</v>
+      </c>
+      <c r="AN24" s="7">
+        <f t="shared" si="98"/>
         <v>0.2</v>
       </c>
-      <c r="AJ24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AO24" s="7">
+        <f t="shared" si="98"/>
         <v>0.2</v>
       </c>
-      <c r="AK24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AP24" s="7">
+        <f t="shared" si="98"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="AQ24" s="7">
+        <f t="shared" si="98"/>
         <v>0.2</v>
       </c>
-      <c r="AL24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AR24" s="7">
+        <f t="shared" si="98"/>
         <v>0.2</v>
       </c>
-      <c r="AM24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AS24" s="7">
+        <f t="shared" si="98"/>
         <v>0.2</v>
       </c>
-      <c r="AN24" s="7">
-        <f t="shared" si="94"/>
+      <c r="AT24" s="7">
+        <f t="shared" ref="AT24" si="99">AT13/AT12</f>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="AU24" s="7">
+        <f t="shared" ref="AU24:AX24" si="100">AU13/AU12</f>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="AV24" s="7">
+        <f t="shared" si="100"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="AW24" s="7">
+        <f t="shared" si="100"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="AX24" s="7">
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
-      <c r="AO24" s="7">
-        <f t="shared" si="94"/>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="AP24" s="7">
-        <f t="shared" ref="AP24" si="95">AP13/AP12</f>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="AQ24" s="7">
-        <f t="shared" ref="AQ24:AT24" si="96">AQ13/AQ12</f>
-        <v>0.2</v>
-      </c>
-      <c r="AR24" s="7">
-        <f t="shared" si="96"/>
-        <v>0.2</v>
-      </c>
-      <c r="AS24" s="7">
-        <f t="shared" si="96"/>
-        <v>0.2</v>
-      </c>
-      <c r="AT24" s="7">
-        <f t="shared" si="96"/>
-        <v>0.2</v>
-      </c>
-      <c r="AV24" s="5" t="s">
+      <c r="AZ24" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AW24" s="6">
+      <c r="BA24" s="6">
         <f>Main!D3</f>
-        <v>1.0980000000000001</v>
+        <v>0.71850000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:49" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:53" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25" s="4" t="s">
@@ -4128,35 +4279,35 @@
         <v>-7.0918367346938793E-2</v>
       </c>
       <c r="E25" s="14">
-        <f t="shared" ref="E25:I25" si="97">E15/E3</f>
+        <f t="shared" ref="E25:I25" si="101">E15/E3</f>
         <v>-0.23259118900994769</v>
       </c>
       <c r="F25" s="14">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>-4.0383846461415435E-2</v>
       </c>
       <c r="G25" s="14">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>-0.11790649808879776</v>
       </c>
       <c r="H25" s="14">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>-1.2722646310432573</v>
       </c>
       <c r="I25" s="14">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>-1.6483679525222552</v>
       </c>
       <c r="J25" s="14">
-        <f t="shared" ref="J25" si="98">J15/J3</f>
+        <f t="shared" ref="J25" si="102">J15/J3</f>
         <v>-0.54838709677419339</v>
       </c>
       <c r="K25" s="14">
-        <f t="shared" ref="K25:L25" si="99">K15/K3</f>
+        <f t="shared" ref="K25:L25" si="103">K15/K3</f>
         <v>-0.40988882387361042</v>
       </c>
       <c r="L25" s="14">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>-0.18983957219251327</v>
       </c>
       <c r="M25" s="14"/>
@@ -4170,92 +4321,108 @@
       <c r="U25" s="14"/>
       <c r="V25" s="14"/>
       <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
+      <c r="X25" s="14">
+        <f t="shared" ref="X25:Y25" si="104">X15/X3</f>
+        <v>-0.51886440044826299</v>
+      </c>
+      <c r="Y25" s="14">
+        <f t="shared" si="104"/>
+        <v>-0.20489114226066205</v>
+      </c>
       <c r="Z25" s="14"/>
       <c r="AA25" s="14"/>
-      <c r="AB25" s="11"/>
+      <c r="AB25" s="14">
+        <f t="shared" ref="AB25:AC25" si="105">AB15/AB3</f>
+        <v>-0.34202650705429671</v>
+      </c>
       <c r="AC25" s="14">
-        <f t="shared" ref="AC25" si="100">AC15/AC3</f>
+        <f t="shared" si="105"/>
+        <v>-0.31156462585034012</v>
+      </c>
+      <c r="AD25" s="14"/>
+      <c r="AE25" s="14"/>
+      <c r="AF25" s="11"/>
+      <c r="AG25" s="14">
+        <f t="shared" ref="AG25" si="106">AG15/AG3</f>
         <v>-5.7181942544459685E-2</v>
       </c>
-      <c r="AD25" s="14">
-        <f t="shared" ref="AD25:AO25" si="101">AD15/AD3</f>
+      <c r="AH25" s="14">
+        <f t="shared" ref="AH25:AS25" si="107">AH15/AH3</f>
         <v>-0.11350646746214786</v>
       </c>
-      <c r="AE25" s="14">
-        <f t="shared" si="101"/>
+      <c r="AI25" s="14">
+        <f t="shared" si="107"/>
         <v>-0.68519123896698286</v>
       </c>
-      <c r="AF25" s="14">
-        <f t="shared" si="101"/>
+      <c r="AJ25" s="14">
+        <f t="shared" si="107"/>
         <v>-0.17492924312973621</v>
       </c>
-      <c r="AG25" s="14">
-        <f t="shared" si="101"/>
+      <c r="AK25" s="14">
+        <f t="shared" si="107"/>
         <v>-0.38262757871878389</v>
       </c>
-      <c r="AH25" s="14">
-        <f t="shared" si="101"/>
+      <c r="AL25" s="14">
+        <f t="shared" si="107"/>
         <v>-0.13969867711905937</v>
       </c>
-      <c r="AI25" s="14">
-        <f t="shared" si="101"/>
-        <v>-0.15987977890526753</v>
-      </c>
-      <c r="AJ25" s="14">
-        <f t="shared" si="101"/>
-        <v>-7.6368628432088775E-2</v>
-      </c>
-      <c r="AK25" s="14">
-        <f t="shared" si="101"/>
-        <v>-2.2157428900875454E-2</v>
-      </c>
-      <c r="AL25" s="14">
-        <f t="shared" si="101"/>
-        <v>1.2598947112351018E-2</v>
-      </c>
       <c r="AM25" s="14">
-        <f t="shared" si="101"/>
-        <v>3.250903764362241E-2</v>
+        <f t="shared" si="107"/>
+        <v>-0.20424269208914697</v>
       </c>
       <c r="AN25" s="14">
-        <f t="shared" si="101"/>
-        <v>4.4299317750944311E-2</v>
+        <f t="shared" si="107"/>
+        <v>-0.10386712410131803</v>
       </c>
       <c r="AO25" s="14">
-        <f t="shared" si="101"/>
-        <v>5.334918824354163E-2</v>
+        <f t="shared" si="107"/>
+        <v>-1.2065587025757295E-2</v>
       </c>
       <c r="AP25" s="14">
-        <f t="shared" ref="AP25" si="102">AP15/AP3</f>
-        <v>5.9891993312630794E-2</v>
+        <f t="shared" si="107"/>
+        <v>3.5758036698952639E-2</v>
       </c>
       <c r="AQ25" s="14">
-        <f t="shared" ref="AQ25:AT25" si="103">AQ15/AQ3</f>
-        <v>6.6257015700024097E-2</v>
+        <f t="shared" si="107"/>
+        <v>6.4120487906361476E-2</v>
       </c>
       <c r="AR25" s="14">
-        <f t="shared" si="103"/>
-        <v>7.2451805380537748E-2</v>
+        <f t="shared" si="107"/>
+        <v>8.1466979523154875E-2</v>
       </c>
       <c r="AS25" s="14">
-        <f t="shared" si="103"/>
-        <v>7.848350261770709E-2</v>
+        <f t="shared" si="107"/>
+        <v>8.8561281241929274E-2</v>
       </c>
       <c r="AT25" s="14">
-        <f t="shared" si="103"/>
-        <v>8.4358861767257057E-2</v>
-      </c>
-      <c r="AV25" s="11" t="s">
+        <f t="shared" ref="AT25" si="108">AT15/AT3</f>
+        <v>9.3519879770081984E-2</v>
+      </c>
+      <c r="AU25" s="14">
+        <f t="shared" ref="AU25:AX25" si="109">AU15/AU3</f>
+        <v>9.8315423051988135E-2</v>
+      </c>
+      <c r="AV25" s="14">
+        <f t="shared" si="109"/>
+        <v>0.10295614726813962</v>
+      </c>
+      <c r="AW25" s="14">
+        <f t="shared" si="109"/>
+        <v>0.10744982194870824</v>
+      </c>
+      <c r="AX25" s="14">
+        <f t="shared" si="109"/>
+        <v>0.11180377701096518</v>
+      </c>
+      <c r="AZ25" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AW25" s="14">
-        <f>AW23/AW24-1</f>
-        <v>-0.45006922200548305</v>
+      <c r="BA25" s="14">
+        <f>BA23/BA24-1</f>
+        <v>-0.3508624801279675</v>
       </c>
     </row>
-    <row r="26" spans="1:49" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:53" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26"/>
@@ -4284,10 +4451,10 @@
       <c r="Z26"/>
       <c r="AA26"/>
       <c r="AB26"/>
-      <c r="AC26" s="7"/>
-      <c r="AD26" s="7"/>
-      <c r="AE26" s="7"/>
-      <c r="AF26" s="7"/>
+      <c r="AC26"/>
+      <c r="AD26"/>
+      <c r="AE26"/>
+      <c r="AF26"/>
       <c r="AG26" s="7"/>
       <c r="AH26" s="7"/>
       <c r="AI26" s="7"/>
@@ -4297,37 +4464,39 @@
       <c r="AM26" s="7"/>
       <c r="AN26" s="7"/>
       <c r="AO26" s="7"/>
-      <c r="AP26" s="4"/>
-      <c r="AQ26" s="4"/>
-      <c r="AR26" s="4"/>
-      <c r="AS26" s="4"/>
+      <c r="AP26" s="7"/>
+      <c r="AQ26" s="7"/>
+      <c r="AR26" s="7"/>
+      <c r="AS26" s="7"/>
       <c r="AT26" s="4"/>
-      <c r="AV26" s="5" t="s">
+      <c r="AU26" s="4"/>
+      <c r="AV26" s="4"/>
+      <c r="AW26" s="4"/>
+      <c r="AX26" s="4"/>
+      <c r="AZ26" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AW26" s="12" t="s">
-        <v>65</v>
+      <c r="BA26" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
-      <c r="AP27" s="5"/>
-      <c r="AQ27" s="5"/>
-      <c r="AR27" s="5"/>
-      <c r="AS27" s="5"/>
       <c r="AT27" s="5"/>
+      <c r="AU27" s="5"/>
+      <c r="AV27" s="5"/>
+      <c r="AW27" s="5"/>
+      <c r="AX27" s="5"/>
     </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:53" x14ac:dyDescent="0.3">
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
-      <c r="AV28" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="AZ28" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
